--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>214.82%</t>
+          <t>249.63%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>21.70</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.55</v>
+        <v>19.45</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.40%</t>
+          <t>10.83%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.25</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.64%</t>
+          <t>-15.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.92%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.7</v>
+        <v>36.95</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>148.24%</t>
+          <t>150.75%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>21.24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>43.55</v>
       </c>
       <c r="D6" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.51%</t>
+          <t>35.10%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.55</v>
+        <v>50.2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.85</v>
+        <v>0.65</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.05%</t>
+          <t>27.47%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.15</v>
+        <v>17.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>174.84%</t>
+          <t>171.50%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.9</v>
+        <v>109.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.49%</t>
+          <t>110.18%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>33.32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.65000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.79%</t>
+          <t>105.08%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>31.57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.8</v>
+        <v>37.93</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>134.27%</t>
+          <t>132.86%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.73%</t>
+          <t>10.41%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.65</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.9</v>
+        <v>16.17</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.00%</t>
+          <t>61.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>34.18</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H683"/>
+  <dimension ref="A1:H694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24879,10 +24879,8 @@
           <t>2.01%</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
+      <c r="H673" t="n">
+        <v>19.73</v>
       </c>
     </row>
     <row r="674">
@@ -24917,11 +24915,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H674" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -24955,10 +24949,8 @@
           <t>10.92%</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>37.50</t>
-        </is>
+      <c r="H675" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="676">
@@ -24993,10 +24985,8 @@
           <t>2.72%</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr">
-        <is>
-          <t>21.09</t>
-        </is>
+      <c r="H676" t="n">
+        <v>21.09</v>
       </c>
     </row>
     <row r="677">
@@ -25031,10 +25021,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
+      <c r="H677" t="n">
+        <v>20.54</v>
       </c>
     </row>
     <row r="678">
@@ -25069,10 +25057,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="H678" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="679">
@@ -25107,10 +25093,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H679" t="inlineStr">
-        <is>
-          <t>32.36</t>
-        </is>
+      <c r="H679" t="n">
+        <v>32.36</v>
       </c>
     </row>
     <row r="680">
@@ -25145,10 +25129,8 @@
           <t>1.48%</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
-        <is>
-          <t>32.71</t>
-        </is>
+      <c r="H680" t="n">
+        <v>32.71</v>
       </c>
     </row>
     <row r="681">
@@ -25183,10 +25165,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H681" t="inlineStr">
-        <is>
-          <t>31.04</t>
-        </is>
+      <c r="H681" t="n">
+        <v>31.04</v>
       </c>
     </row>
     <row r="682">
@@ -25221,10 +25201,8 @@
           <t>10.73%</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr">
-        <is>
-          <t>29.74</t>
-        </is>
+      <c r="H682" t="n">
+        <v>29.74</v>
       </c>
     </row>
     <row r="683">
@@ -25259,9 +25237,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H683" t="inlineStr">
-        <is>
-          <t>33.61</t>
+      <c r="H683" t="n">
+        <v>33.61</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>143</v>
+      </c>
+      <c r="D684" t="n">
+        <v>13</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>249.63%</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D685" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>29</v>
+      </c>
+      <c r="D686" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-15.78%</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>150.75%</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>35.10%</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>20.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>27.47%</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>21.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="D690" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>171.50%</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>32.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="D691" t="n">
+        <v>2</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>110.18%</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>33.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>1.73%</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>105.08%</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>31.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="D693" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>132.86%</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>10.41%</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>61.70%</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>34.18</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>-6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>249.63%</t>
+          <t>234.96%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>20.79</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.45</v>
+        <v>18.75</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.83%</t>
+          <t>6.84%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.65</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.78%</t>
+          <t>-16.80%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.15%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>36.73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.95</v>
+        <v>37.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>150.75%</t>
+          <t>153.13%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43.55</v>
+        <v>45.55</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>35.10%</t>
+          <t>41.31%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>21.49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.47%</t>
+          <t>28.48%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>21.44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.05</v>
+        <v>16.9</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>171.50%</t>
+          <t>169.11%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>31.89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.9</v>
+        <v>109.65</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.18%</t>
+          <t>109.70%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>33.24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>94.25</v>
+        <v>93.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>-0.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.08%</t>
+          <t>103.88%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>31.39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.93</v>
+        <v>37.61</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13</v>
+        <v>-0.32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>132.86%</t>
+          <t>130.89%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.41%</t>
+          <t>10.50%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.17</v>
+        <v>16.12</v>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.70%</t>
+          <t>61.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.07</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H694"/>
+  <dimension ref="A1:H705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25273,10 +25273,8 @@
           <t>1.82%</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>21.70</t>
-        </is>
+      <c r="H684" t="n">
+        <v>21.7</v>
       </c>
     </row>
     <row r="685">
@@ -25311,11 +25309,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -25349,10 +25343,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H686" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="687">
@@ -25387,10 +25379,8 @@
           <t>2.71%</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
+      <c r="H687" t="n">
+        <v>21.24</v>
       </c>
     </row>
     <row r="688">
@@ -25425,10 +25415,8 @@
           <t>3.21%</t>
         </is>
       </c>
-      <c r="H688" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
+      <c r="H688" t="n">
+        <v>20.54</v>
       </c>
     </row>
     <row r="689">
@@ -25463,10 +25451,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H689" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
+      <c r="H689" t="n">
+        <v>21.27</v>
       </c>
     </row>
     <row r="690">
@@ -25501,10 +25487,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H690" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="H690" t="n">
+        <v>32.17</v>
       </c>
     </row>
     <row r="691">
@@ -25539,10 +25523,8 @@
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr">
-        <is>
-          <t>33.32</t>
-        </is>
+      <c r="H691" t="n">
+        <v>33.32</v>
       </c>
     </row>
     <row r="692">
@@ -25577,10 +25559,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H692" t="inlineStr">
-        <is>
-          <t>31.57</t>
-        </is>
+      <c r="H692" t="n">
+        <v>31.57</v>
       </c>
     </row>
     <row r="693">
@@ -25615,10 +25595,8 @@
           <t>10.41%</t>
         </is>
       </c>
-      <c r="H693" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="H693" t="n">
+        <v>30.65</v>
       </c>
     </row>
     <row r="694">
@@ -25653,9 +25631,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H694" t="inlineStr">
-        <is>
-          <t>34.18</t>
+      <c r="H694" t="n">
+        <v>34.18</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>137</v>
+      </c>
+      <c r="D695" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-4.2%</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>234.96%</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D696" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-3.6%</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>6.84%</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="D697" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-16.80%</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>11.15%</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>36.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D698" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>153.13%</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>21.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="D699" t="n">
+        <v>2</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>41.31%</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>21.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>28.48%</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>21.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D701" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>169.11%</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>31.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="D702" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>109.70%</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>33.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D703" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>103.88%</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>31.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="D704" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>130.89%</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>10.50%</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>30.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>61.20%</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>34.07</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-6</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>234.96%</t>
+          <t>247.22%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>21.47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.75</v>
+        <v>19.15</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6.84%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.65</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.35</v>
+        <v>0.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.80%</t>
+          <t>-15.13%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.15%</t>
+          <t>11.09%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.3</v>
+        <v>36.75</v>
       </c>
       <c r="D5" t="n">
-        <v>0.35</v>
+        <v>-0.55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>153.13%</t>
+          <t>150.22%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.55</v>
+        <v>44.25</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>-1.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.31%</t>
+          <t>36.06%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>20.87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.48%</t>
+          <t>26.03%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9</v>
+        <v>16.95</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>169.11%</t>
+          <t>172.51%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>31.98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -752,16 +752,16 @@
         <v>109.65</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.70%</t>
+          <t>107.56%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.88%</t>
+          <t>101.90%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.61</v>
+        <v>37.74</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>130.89%</t>
+          <t>130.20%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>10.47%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>30.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.12</v>
+        <v>16.11</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.20%</t>
+          <t>61.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.05</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H705"/>
+  <dimension ref="A1:H716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25667,10 +25667,8 @@
           <t>1.90%</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
+      <c r="H695" t="n">
+        <v>20.79</v>
       </c>
     </row>
     <row r="696">
@@ -25705,11 +25703,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H696" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -25743,10 +25737,8 @@
           <t>11.15%</t>
         </is>
       </c>
-      <c r="H697" t="inlineStr">
-        <is>
-          <t>36.73</t>
-        </is>
+      <c r="H697" t="n">
+        <v>36.73</v>
       </c>
     </row>
     <row r="698">
@@ -25781,10 +25773,8 @@
           <t>2.68%</t>
         </is>
       </c>
-      <c r="H698" t="inlineStr">
-        <is>
-          <t>21.44</t>
-        </is>
+      <c r="H698" t="n">
+        <v>21.44</v>
       </c>
     </row>
     <row r="699">
@@ -25819,10 +25809,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H699" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
+      <c r="H699" t="n">
+        <v>21.49</v>
       </c>
     </row>
     <row r="700">
@@ -25857,10 +25845,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H700" t="inlineStr">
-        <is>
-          <t>21.44</t>
-        </is>
+      <c r="H700" t="n">
+        <v>21.44</v>
       </c>
     </row>
     <row r="701">
@@ -25895,10 +25881,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H701" t="inlineStr">
-        <is>
-          <t>31.89</t>
-        </is>
+      <c r="H701" t="n">
+        <v>31.89</v>
       </c>
     </row>
     <row r="702">
@@ -25933,10 +25917,8 @@
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H702" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
+      <c r="H702" t="n">
+        <v>33.24</v>
       </c>
     </row>
     <row r="703">
@@ -25971,10 +25953,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr">
-        <is>
-          <t>31.39</t>
-        </is>
+      <c r="H703" t="n">
+        <v>31.39</v>
       </c>
     </row>
     <row r="704">
@@ -26009,10 +25989,8 @@
           <t>10.50%</t>
         </is>
       </c>
-      <c r="H704" t="inlineStr">
-        <is>
-          <t>30.39</t>
-        </is>
+      <c r="H704" t="n">
+        <v>30.39</v>
       </c>
     </row>
     <row r="705">
@@ -26047,9 +26025,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H705" t="inlineStr">
-        <is>
-          <t>34.07</t>
+      <c r="H705" t="n">
+        <v>34.07</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D706" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>247.22%</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>21.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-15.13%</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>11.09%</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>36.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="D709" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>150.22%</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>2.72%</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>21.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="D710" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-2.85%</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>36.06%</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>20.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D711" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>26.03%</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>21.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>172.51%</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>31.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="D713" t="n">
+        <v>0</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>107.56%</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>33.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D714" t="n">
+        <v>0</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>101.90%</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>31.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="D715" t="n">
+        <v>0</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>130.20%</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>10.47%</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>30.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="D716" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>61.10%</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>34.05</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141.5</v>
+        <v>142.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>247.22%</t>
+          <t>251.37%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.15</v>
+        <v>18.85</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.13%</t>
+          <t>-15.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.75</v>
+        <v>37.2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.55</v>
+        <v>0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>150.22%</t>
+          <t>152.45%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.25</v>
+        <v>44.95</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.06%</t>
+          <t>38.62%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>21.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.03%</t>
+          <t>24.57%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.95</v>
+        <v>16.65</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>172.51%</t>
+          <t>170.29%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>31.42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.65</v>
+        <v>109.15</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107.56%</t>
+          <t>102.66%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.59999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.90%</t>
+          <t>97.68%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.74</v>
+        <v>37.72</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>130.20%</t>
+          <t>128.73%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -847,14 +847,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>30.48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.11</v>
+        <v>16.03</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.10%</t>
+          <t>60.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>33.88</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H716"/>
+  <dimension ref="A1:H727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26061,10 +26061,8 @@
           <t>1.84%</t>
         </is>
       </c>
-      <c r="H706" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
+      <c r="H706" t="n">
+        <v>21.47</v>
       </c>
     </row>
     <row r="707">
@@ -26099,11 +26097,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H707" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -26137,10 +26131,8 @@
           <t>11.09%</t>
         </is>
       </c>
-      <c r="H708" t="inlineStr">
-        <is>
-          <t>36.92</t>
-        </is>
+      <c r="H708" t="n">
+        <v>36.92</v>
       </c>
     </row>
     <row r="709">
@@ -26175,10 +26167,8 @@
           <t>2.72%</t>
         </is>
       </c>
-      <c r="H709" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
+      <c r="H709" t="n">
+        <v>21.12</v>
       </c>
     </row>
     <row r="710">
@@ -26213,10 +26203,8 @@
           <t>3.16%</t>
         </is>
       </c>
-      <c r="H710" t="inlineStr">
-        <is>
-          <t>20.87</t>
-        </is>
+      <c r="H710" t="n">
+        <v>20.87</v>
       </c>
     </row>
     <row r="711">
@@ -26251,10 +26239,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H711" t="inlineStr">
-        <is>
-          <t>21.31</t>
-        </is>
+      <c r="H711" t="n">
+        <v>21.31</v>
       </c>
     </row>
     <row r="712">
@@ -26289,10 +26275,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H712" t="inlineStr">
-        <is>
-          <t>31.98</t>
-        </is>
+      <c r="H712" t="n">
+        <v>31.98</v>
       </c>
     </row>
     <row r="713">
@@ -26327,10 +26311,8 @@
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H713" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
+      <c r="H713" t="n">
+        <v>33.24</v>
       </c>
     </row>
     <row r="714">
@@ -26365,10 +26347,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H714" t="inlineStr">
-        <is>
-          <t>31.35</t>
-        </is>
+      <c r="H714" t="n">
+        <v>31.35</v>
       </c>
     </row>
     <row r="715">
@@ -26403,10 +26383,8 @@
           <t>10.47%</t>
         </is>
       </c>
-      <c r="H715" t="inlineStr">
-        <is>
-          <t>30.50</t>
-        </is>
+      <c r="H715" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="716">
@@ -26441,9 +26419,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>34.05</t>
+      <c r="H716" t="n">
+        <v>34.05</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D717" t="n">
+        <v>1</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>251.37%</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>21.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D718" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>-1.57%</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>8.96%</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>29</v>
+      </c>
+      <c r="D719" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>-15.78%</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="D720" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>152.45%</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>21.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="D721" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>38.62%</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>21.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D722" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>24.57%</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>21.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D723" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>-1.77%</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>170.29%</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>31.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="D724" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>102.66%</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>33.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="D725" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>97.68%</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>31.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="D726" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>128.73%</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>10.47%</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="D727" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>60.30%</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>33.88</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>251.37%</t>
+          <t>249.40%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.85</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.57%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>13.43%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.78%</t>
+          <t>-14.45%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.13%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>36.79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.2</v>
+        <v>37.85</v>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>152.45%</t>
+          <t>161.14%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.95</v>
+        <v>46.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>1.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.62%</t>
+          <t>42.36%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.20</t>
+          <t>21.84</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.9</v>
+        <v>51.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.57%</t>
+          <t>29.22%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65</v>
+        <v>16.4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.77%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>170.29%</t>
+          <t>173.33%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>30.94</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.15</v>
+        <v>107.7</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.66%</t>
+          <t>98.17%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>32.65</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.25</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.68%</t>
+          <t>94.81%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>30.85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.72</v>
+        <v>37.07</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.73%</t>
+          <t>126.96%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>10.66%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>29.96</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.03</v>
+        <v>15.88</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.30%</t>
+          <t>58.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.57</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H727"/>
+  <dimension ref="A1:H738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26455,10 +26455,8 @@
           <t>1.83%</t>
         </is>
       </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>21.62</t>
-        </is>
+      <c r="H717" t="n">
+        <v>21.62</v>
       </c>
     </row>
     <row r="718">
@@ -26493,11 +26491,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -26531,10 +26525,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H719" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H719" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="720">
@@ -26569,10 +26561,8 @@
           <t>2.69%</t>
         </is>
       </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>21.38</t>
-        </is>
+      <c r="H720" t="n">
+        <v>21.38</v>
       </c>
     </row>
     <row r="721">
@@ -26607,10 +26597,8 @@
           <t>3.11%</t>
         </is>
       </c>
-      <c r="H721" t="inlineStr">
-        <is>
-          <t>21.20</t>
-        </is>
+      <c r="H721" t="n">
+        <v>21.2</v>
       </c>
     </row>
     <row r="722">
@@ -26645,10 +26633,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>21.14</t>
-        </is>
+      <c r="H722" t="n">
+        <v>21.14</v>
       </c>
     </row>
     <row r="723">
@@ -26683,10 +26669,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>31.42</t>
-        </is>
+      <c r="H723" t="n">
+        <v>31.42</v>
       </c>
     </row>
     <row r="724">
@@ -26721,10 +26705,8 @@
           <t>1.47%</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
+      <c r="H724" t="n">
+        <v>33.09</v>
       </c>
     </row>
     <row r="725">
@@ -26759,10 +26741,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H725" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
+      <c r="H725" t="n">
+        <v>31.24</v>
       </c>
     </row>
     <row r="726">
@@ -26797,10 +26777,8 @@
           <t>10.47%</t>
         </is>
       </c>
-      <c r="H726" t="inlineStr">
-        <is>
-          <t>30.48</t>
-        </is>
+      <c r="H726" t="n">
+        <v>30.48</v>
       </c>
     </row>
     <row r="727">
@@ -26835,9 +26813,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H727" t="inlineStr">
-        <is>
-          <t>33.88</t>
+      <c r="H727" t="n">
+        <v>33.88</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="D728" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>249.40%</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>1.86%</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>19</v>
+      </c>
+      <c r="D729" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>13.43%</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D730" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-14.45%</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>11.13%</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>36.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="D731" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>161.14%</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>2.64%</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="D732" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>42.36%</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>21.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="D733" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>29.22%</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>21.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D734" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-1.5%</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>173.33%</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>30.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="D735" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>98.17%</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="D736" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>94.81%</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="D737" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>126.96%</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>10.66%</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>29.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="D738" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>58.80%</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>33.57</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>140.5</v>
+        <v>142.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>249.40%</t>
+          <t>252.65%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.43%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>28.75</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.45%</t>
+          <t>-17.57%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.13%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.85</v>
+        <v>38.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>161.14%</t>
+          <t>164.17%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>22.30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.3</v>
+        <v>46.35</v>
       </c>
       <c r="D6" t="n">
-        <v>1.35</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.36%</t>
+          <t>44.00%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.22%</t>
+          <t>31.38%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>22.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173.33%</t>
+          <t>172.13%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>31.32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.7</v>
+        <v>106.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.17%</t>
+          <t>94.77%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.09999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.81%</t>
+          <t>92.21%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.67</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.07</v>
+        <v>37.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>126.96%</t>
+          <t>122.59%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.66%</t>
+          <t>10.65%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>29.98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.88</v>
+        <v>15.82</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.80%</t>
+          <t>58.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>33.44</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H738"/>
+  <dimension ref="A1:H749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26849,10 +26849,8 @@
           <t>1.86%</t>
         </is>
       </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
+      <c r="H728" t="n">
+        <v>21.35</v>
       </c>
     </row>
     <row r="729">
@@ -26887,11 +26885,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -26925,10 +26919,8 @@
           <t>11.13%</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>36.79</t>
-        </is>
+      <c r="H730" t="n">
+        <v>36.79</v>
       </c>
     </row>
     <row r="731">
@@ -26963,10 +26955,8 @@
           <t>2.64%</t>
         </is>
       </c>
-      <c r="H731" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="H731" t="n">
+        <v>21.75</v>
       </c>
     </row>
     <row r="732">
@@ -27001,10 +26991,8 @@
           <t>3.02%</t>
         </is>
       </c>
-      <c r="H732" t="inlineStr">
-        <is>
-          <t>21.84</t>
-        </is>
+      <c r="H732" t="n">
+        <v>21.84</v>
       </c>
     </row>
     <row r="733">
@@ -27039,10 +27027,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H733" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
+      <c r="H733" t="n">
+        <v>21.91</v>
       </c>
     </row>
     <row r="734">
@@ -27077,10 +27063,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H734" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="H734" t="n">
+        <v>30.94</v>
       </c>
     </row>
     <row r="735">
@@ -27115,10 +27099,8 @@
           <t>1.49%</t>
         </is>
       </c>
-      <c r="H735" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="H735" t="n">
+        <v>32.65</v>
       </c>
     </row>
     <row r="736">
@@ -27153,10 +27135,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H736" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="H736" t="n">
+        <v>30.85</v>
       </c>
     </row>
     <row r="737">
@@ -27191,10 +27171,8 @@
           <t>10.66%</t>
         </is>
       </c>
-      <c r="H737" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="H737" t="n">
+        <v>29.96</v>
       </c>
     </row>
     <row r="738">
@@ -27229,9 +27207,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>33.57</t>
+      <c r="H738" t="n">
+        <v>33.57</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D739" t="n">
+        <v>2</v>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>252.65%</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>21.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D740" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D741" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-17.57%</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D742" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>164.17%</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>22.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="D743" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>44.00%</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>21.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D744" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>31.38%</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D745" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>172.13%</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D746" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>94.77%</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>32.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="D747" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>92.21%</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>30.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D748" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>122.59%</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>10.65%</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>29.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="D749" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>58.20%</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>33.44</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142.5</v>
+        <v>138.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>252.65%</t>
+          <t>242.75%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="D3" t="n">
         <v>-0.1</v>
@@ -533,7 +533,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.50%</t>
+          <t>11.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.75</v>
+        <v>28.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.57%</t>
+          <t>-18.86%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>11.29%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.8</v>
+        <v>38.15</v>
       </c>
       <c r="D5" t="n">
-        <v>0.95</v>
+        <v>-0.65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>164.17%</t>
+          <t>159.75%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>21.93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.35</v>
+        <v>45.65</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.00%</t>
+          <t>41.83%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.38%</t>
+          <t>29.63%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.6</v>
+        <v>16.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>-0.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>172.13%</t>
+          <t>163.11%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>30.28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.9</v>
+        <v>106.25</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94.77%</t>
+          <t>93.58%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>32.21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.55</v>
+        <v>90.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>92.21%</t>
+          <t>90.95%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.1</v>
+        <v>36.63</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>122.59%</t>
+          <t>119.77%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.65%</t>
+          <t>10.78%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>29.60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.82</v>
+        <v>15.75</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.20%</t>
+          <t>57.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>33.29</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H749"/>
+  <dimension ref="A1:H760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27243,10 +27243,8 @@
           <t>1.83%</t>
         </is>
       </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>21.62</t>
-        </is>
+      <c r="H739" t="n">
+        <v>21.62</v>
       </c>
     </row>
     <row r="740">
@@ -27281,11 +27279,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H740" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -27319,10 +27313,8 @@
           <t>11.11%</t>
         </is>
       </c>
-      <c r="H741" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="H741" t="n">
+        <v>36.86</v>
       </c>
     </row>
     <row r="742">
@@ -27357,10 +27349,8 @@
           <t>2.58%</t>
         </is>
       </c>
-      <c r="H742" t="inlineStr">
-        <is>
-          <t>22.30</t>
-        </is>
+      <c r="H742" t="n">
+        <v>22.3</v>
       </c>
     </row>
     <row r="743">
@@ -27395,10 +27385,8 @@
           <t>3.02%</t>
         </is>
       </c>
-      <c r="H743" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="H743" t="n">
+        <v>21.86</v>
       </c>
     </row>
     <row r="744">
@@ -27433,10 +27421,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H744" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
+      <c r="H744" t="n">
+        <v>22.25</v>
       </c>
     </row>
     <row r="745">
@@ -27471,10 +27457,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
+      <c r="H745" t="n">
+        <v>31.32</v>
       </c>
     </row>
     <row r="746">
@@ -27509,10 +27493,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H746" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="H746" t="n">
+        <v>32.41</v>
       </c>
     </row>
     <row r="747">
@@ -27547,10 +27529,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H747" t="inlineStr">
-        <is>
-          <t>30.67</t>
-        </is>
+      <c r="H747" t="n">
+        <v>30.67</v>
       </c>
     </row>
     <row r="748">
@@ -27585,10 +27565,8 @@
           <t>10.65%</t>
         </is>
       </c>
-      <c r="H748" t="inlineStr">
-        <is>
-          <t>29.98</t>
-        </is>
+      <c r="H748" t="n">
+        <v>29.98</v>
       </c>
     </row>
     <row r="749">
@@ -27623,9 +27601,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H749" t="inlineStr">
-        <is>
-          <t>33.44</t>
+      <c r="H749" t="n">
+        <v>33.44</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="D750" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>242.75%</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D751" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>11.90%</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D752" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-1.57%</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-18.86%</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>11.29%</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>36.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D753" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-1.68%</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>159.75%</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>21.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="D754" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>41.83%</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>21.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="D755" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-1.33%</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>29.63%</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="D756" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-3.31%</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>163.11%</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>30.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="D757" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>93.58%</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>32.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="D758" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>90.95%</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>30.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="D759" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>119.77%</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>10.78%</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>29.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="D760" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>57.50%</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>33.29</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>138.5</v>
+        <v>142</v>
       </c>
       <c r="D2" t="n">
-        <v>-4</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>242.75%</t>
+          <t>251.84%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.8</v>
+        <v>19.35</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1</v>
+        <v>0.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.90%</t>
+          <t>14.50%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.3</v>
+        <v>29.15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.45</v>
+        <v>0.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.57%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-18.86%</t>
+          <t>-15.75%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.29%</t>
+          <t>10.96%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>37.37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.15</v>
+        <v>39.15</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.65</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>159.75%</t>
+          <t>167.44%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>22.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.65</v>
+        <v>46.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.83%</t>
+          <t>44.96%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.91</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.63%</t>
+          <t>27.99%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.05</v>
+        <v>16.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.55</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>163.11%</t>
+          <t>165.04%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>30.75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.25</v>
+        <v>106.9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>93.58%</t>
+          <t>92.19%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90.95</v>
+        <v>91.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>90.95%</t>
+          <t>90.50%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.65</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.63</v>
+        <v>37.21</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>119.77%</t>
+          <t>118.19%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.78%</t>
+          <t>10.62%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>30.07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.75</v>
+        <v>15.89</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.50%</t>
+          <t>58.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.29</t>
+          <t>33.59</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H760"/>
+  <dimension ref="A1:H771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27637,10 +27637,8 @@
           <t>1.88%</t>
         </is>
       </c>
-      <c r="H750" t="inlineStr">
-        <is>
-          <t>21.05</t>
-        </is>
+      <c r="H750" t="n">
+        <v>21.05</v>
       </c>
     </row>
     <row r="751">
@@ -27675,11 +27673,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H751" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -27713,10 +27707,8 @@
           <t>11.29%</t>
         </is>
       </c>
-      <c r="H752" t="inlineStr">
-        <is>
-          <t>36.28</t>
-        </is>
+      <c r="H752" t="n">
+        <v>36.28</v>
       </c>
     </row>
     <row r="753">
@@ -27751,10 +27743,8 @@
           <t>2.62%</t>
         </is>
       </c>
-      <c r="H753" t="inlineStr">
-        <is>
-          <t>21.93</t>
-        </is>
+      <c r="H753" t="n">
+        <v>21.93</v>
       </c>
     </row>
     <row r="754">
@@ -27789,10 +27779,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H754" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
+      <c r="H754" t="n">
+        <v>21.53</v>
       </c>
     </row>
     <row r="755">
@@ -27827,10 +27815,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H755" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="H755" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="756">
@@ -27865,10 +27851,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H756" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
+      <c r="H756" t="n">
+        <v>30.28</v>
       </c>
     </row>
     <row r="757">
@@ -27903,10 +27887,8 @@
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H757" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
+      <c r="H757" t="n">
+        <v>32.21</v>
       </c>
     </row>
     <row r="758">
@@ -27941,10 +27923,8 @@
           <t>3.52%</t>
         </is>
       </c>
-      <c r="H758" t="inlineStr">
-        <is>
-          <t>30.47</t>
-        </is>
+      <c r="H758" t="n">
+        <v>30.47</v>
       </c>
     </row>
     <row r="759">
@@ -27979,10 +27959,8 @@
           <t>10.78%</t>
         </is>
       </c>
-      <c r="H759" t="inlineStr">
-        <is>
-          <t>29.60</t>
-        </is>
+      <c r="H759" t="n">
+        <v>29.6</v>
       </c>
     </row>
     <row r="760">
@@ -28017,9 +27995,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H760" t="inlineStr">
-        <is>
-          <t>33.29</t>
+      <c r="H760" t="n">
+        <v>33.29</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>142</v>
+      </c>
+      <c r="D761" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>251.84%</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="D762" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>14.50%</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="D763" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>-15.75%</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="D764" t="n">
+        <v>1</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>167.44%</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="D765" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>44.96%</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>3.01%</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>21.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D766" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>27.99%</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>21.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D767" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>165.04%</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D768" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>92.19%</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>32.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D769" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>90.50%</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="D770" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>118.19%</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>10.62%</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>30.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="D771" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>58.90%</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>33.59</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142</v>
+        <v>147.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>251.84%</t>
+          <t>261.94%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>22.38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.35</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.55</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>13.78%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.15</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.75%</t>
+          <t>-14.68%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.15</v>
+        <v>39.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>167.44%</t>
+          <t>171.75%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>22.79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.45</v>
+        <v>47.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.96%</t>
+          <t>48.73%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>22.31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.99%</t>
+          <t>30.51%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>21.99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>16.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>165.04%</t>
+          <t>153.89%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.9</v>
+        <v>108.05</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.19%</t>
+          <t>95.64%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>32.76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.5</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>90.50%</t>
+          <t>93.04%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.21</v>
+        <v>37.6</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>118.19%</t>
+          <t>121.50%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.62%</t>
+          <t>10.51%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>30.38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.89</v>
+        <v>16.04</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58.90%</t>
+          <t>60.40%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>33.90</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H771"/>
+  <dimension ref="A1:H782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28031,10 +28031,8 @@
           <t>1.84%</t>
         </is>
       </c>
-      <c r="H761" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
+      <c r="H761" t="n">
+        <v>21.55</v>
       </c>
     </row>
     <row r="762">
@@ -28069,11 +28067,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H762" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -28107,10 +28101,8 @@
           <t>10.96%</t>
         </is>
       </c>
-      <c r="H763" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
+      <c r="H763" t="n">
+        <v>37.37</v>
       </c>
     </row>
     <row r="764">
@@ -28145,10 +28137,8 @@
           <t>2.55%</t>
         </is>
       </c>
-      <c r="H764" t="inlineStr">
-        <is>
-          <t>22.50</t>
-        </is>
+      <c r="H764" t="n">
+        <v>22.5</v>
       </c>
     </row>
     <row r="765">
@@ -28183,10 +28173,8 @@
           <t>3.01%</t>
         </is>
       </c>
-      <c r="H765" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
+      <c r="H765" t="n">
+        <v>21.91</v>
       </c>
     </row>
     <row r="766">
@@ -28221,10 +28209,8 @@
           <t>3.44%</t>
         </is>
       </c>
-      <c r="H766" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
+      <c r="H766" t="n">
+        <v>21.57</v>
       </c>
     </row>
     <row r="767">
@@ -28259,10 +28245,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H767" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
+      <c r="H767" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="768">
@@ -28297,10 +28281,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H768" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="H768" t="n">
+        <v>32.41</v>
       </c>
     </row>
     <row r="769">
@@ -28335,10 +28317,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H769" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="H769" t="n">
+        <v>30.65</v>
       </c>
     </row>
     <row r="770">
@@ -28373,10 +28353,8 @@
           <t>10.62%</t>
         </is>
       </c>
-      <c r="H770" t="inlineStr">
-        <is>
-          <t>30.07</t>
-        </is>
+      <c r="H770" t="n">
+        <v>30.07</v>
       </c>
     </row>
     <row r="771">
@@ -28411,9 +28389,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H771" t="inlineStr">
-        <is>
-          <t>33.59</t>
+      <c r="H771" t="n">
+        <v>33.59</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D772" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>261.94%</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>22.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D773" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>13.78%</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>29</v>
+      </c>
+      <c r="D774" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>-14.68%</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="D775" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>171.75%</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>22.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D776" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>48.73%</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>22.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="D777" t="n">
+        <v>1</v>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>30.51%</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D778" t="n">
+        <v>0</v>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>153.89%</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="D779" t="n">
+        <v>0</v>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>95.64%</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>32.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="D780" t="n">
+        <v>0</v>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>93.04%</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>30.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D781" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>121.50%</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>10.51%</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>30.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="D782" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>60.40%</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>33.90</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>147.5</v>
+        <v>156</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>5.76%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>261.94%</t>
+          <t>279.59%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>23.67</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.4</v>
+        <v>19.45</v>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
@@ -533,7 +533,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.78%</t>
+          <t>10.83%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.68%</t>
+          <t>-14.09%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>10.94%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>37.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.65</v>
+        <v>39.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>171.75%</t>
+          <t>168.46%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>22.59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.3</v>
+        <v>46.4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.73%</t>
+          <t>45.02%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>21.89</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.9</v>
+        <v>51.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.51%</t>
+          <t>27.88%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>21.65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.3</v>
+        <v>17.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>153.89%</t>
+          <t>148.91%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>32.26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.05</v>
+        <v>109.85</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>95.64%</t>
+          <t>96.80%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>33.31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.15000000000001</v>
+        <v>93.75</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93.04%</t>
+          <t>94.41%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>31.41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.6</v>
+        <v>38.73</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>121.50%</t>
+          <t>123.30%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.20%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>31.30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.04</v>
+        <v>16.25</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.40%</t>
+          <t>62.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.90</t>
+          <t>34.35</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H782"/>
+  <dimension ref="A1:H793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28425,10 +28425,8 @@
           <t>1.77%</t>
         </is>
       </c>
-      <c r="H772" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
+      <c r="H772" t="n">
+        <v>22.38</v>
       </c>
     </row>
     <row r="773">
@@ -28463,11 +28461,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H773" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -28501,10 +28495,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H774" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H774" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="775">
@@ -28539,10 +28531,8 @@
           <t>2.52%</t>
         </is>
       </c>
-      <c r="H775" t="inlineStr">
-        <is>
-          <t>22.79</t>
-        </is>
+      <c r="H775" t="n">
+        <v>22.79</v>
       </c>
     </row>
     <row r="776">
@@ -28577,10 +28567,8 @@
           <t>2.96%</t>
         </is>
       </c>
-      <c r="H776" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
+      <c r="H776" t="n">
+        <v>22.31</v>
       </c>
     </row>
     <row r="777">
@@ -28615,10 +28603,8 @@
           <t>3.37%</t>
         </is>
       </c>
-      <c r="H777" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
+      <c r="H777" t="n">
+        <v>21.99</v>
       </c>
     </row>
     <row r="778">
@@ -28653,10 +28639,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H778" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
+      <c r="H778" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="779">
@@ -28691,10 +28675,8 @@
           <t>1.48%</t>
         </is>
       </c>
-      <c r="H779" t="inlineStr">
-        <is>
-          <t>32.76</t>
-        </is>
+      <c r="H779" t="n">
+        <v>32.76</v>
       </c>
     </row>
     <row r="780">
@@ -28729,10 +28711,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H780" t="inlineStr">
-        <is>
-          <t>30.87</t>
-        </is>
+      <c r="H780" t="n">
+        <v>30.87</v>
       </c>
     </row>
     <row r="781">
@@ -28767,10 +28747,8 @@
           <t>10.51%</t>
         </is>
       </c>
-      <c r="H781" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
+      <c r="H781" t="n">
+        <v>30.38</v>
       </c>
     </row>
     <row r="782">
@@ -28805,9 +28783,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H782" t="inlineStr">
-        <is>
-          <t>33.90</t>
+      <c r="H782" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>156</v>
+      </c>
+      <c r="D783" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>5.76%</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>279.59%</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>23.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D784" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D785" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>-14.09%</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>37.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="D786" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>168.46%</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>22.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="D787" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>45.02%</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>21.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="D788" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>27.88%</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D789" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>148.91%</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>32.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="D790" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>96.80%</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="D791" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>94.41%</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>31.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>123.30%</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>10.20%</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>31.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="D793" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>62.50%</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>34.35</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>279.59%</t>
+          <t>270.93%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.86</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.45</v>
+        <v>20.55</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>5.66%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.83%</t>
+          <t>15.77%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-14.09%</t>
+          <t>-9.83%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>10.79%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.95</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.3</v>
+        <v>40.45</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.35</v>
+        <v>1.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>168.46%</t>
+          <t>177.23%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>23.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.02%</t>
+          <t>43.54%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>51.1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.88%</t>
+          <t>27.42%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>148.91%</t>
+          <t>159.91%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>33.40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109.85</v>
+        <v>111.35</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.80%</t>
+          <t>97.92%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>33.76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.75</v>
+        <v>95.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.41%</t>
+          <t>97.04%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>31.92</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.73</v>
+        <v>39.35</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>123.30%</t>
+          <t>124.71%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.20%</t>
+          <t>10.04%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31.30</t>
+          <t>31.80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.25</v>
+        <v>16.47</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.50%</t>
+          <t>64.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.81</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H793"/>
+  <dimension ref="A1:H804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28819,10 +28819,8 @@
           <t>1.67%</t>
         </is>
       </c>
-      <c r="H783" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
+      <c r="H783" t="n">
+        <v>23.67</v>
       </c>
     </row>
     <row r="784">
@@ -28857,11 +28855,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H784" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -28895,10 +28889,8 @@
           <t>10.94%</t>
         </is>
       </c>
-      <c r="H785" t="inlineStr">
-        <is>
-          <t>37.44</t>
-        </is>
+      <c r="H785" t="n">
+        <v>37.44</v>
       </c>
     </row>
     <row r="786">
@@ -28933,10 +28925,8 @@
           <t>2.54%</t>
         </is>
       </c>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
+      <c r="H786" t="n">
+        <v>22.59</v>
       </c>
     </row>
     <row r="787">
@@ -28971,10 +28961,8 @@
           <t>3.02%</t>
         </is>
       </c>
-      <c r="H787" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
+      <c r="H787" t="n">
+        <v>21.89</v>
       </c>
     </row>
     <row r="788">
@@ -29009,10 +28997,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H788" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
+      <c r="H788" t="n">
+        <v>21.65</v>
       </c>
     </row>
     <row r="789">
@@ -29047,10 +29033,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H789" t="inlineStr">
-        <is>
-          <t>32.26</t>
-        </is>
+      <c r="H789" t="n">
+        <v>32.26</v>
       </c>
     </row>
     <row r="790">
@@ -29085,10 +29069,8 @@
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H790" t="inlineStr">
-        <is>
-          <t>33.31</t>
-        </is>
+      <c r="H790" t="n">
+        <v>33.31</v>
       </c>
     </row>
     <row r="791">
@@ -29123,10 +29105,8 @@
           <t>3.41%</t>
         </is>
       </c>
-      <c r="H791" t="inlineStr">
-        <is>
-          <t>31.41</t>
-        </is>
+      <c r="H791" t="n">
+        <v>31.41</v>
       </c>
     </row>
     <row r="792">
@@ -29161,10 +29141,8 @@
           <t>10.20%</t>
         </is>
       </c>
-      <c r="H792" t="inlineStr">
-        <is>
-          <t>31.30</t>
-        </is>
+      <c r="H792" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="793">
@@ -29199,9 +29177,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H793" t="inlineStr">
-        <is>
-          <t>34.35</t>
+      <c r="H793" t="n">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>157</v>
+      </c>
+      <c r="D794" t="n">
+        <v>1</v>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>270.93%</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>23.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="D795" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>5.66%</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>15.77%</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>-9.83%</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>10.79%</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="D797" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>177.23%</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>2.47%</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D798" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>43.54%</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>21.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="D799" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>27.42%</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D800" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>159.91%</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>33.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="D801" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>97.92%</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>33.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="D802" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>97.04%</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>31.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="D803" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>124.71%</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>10.04%</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>31.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="D804" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>64.70%</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>34.81</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>270.93%</t>
+          <t>278.02%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>24.28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.55</v>
+        <v>20.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1</v>
+        <v>-0.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.77%</t>
+          <t>13.80%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.83%</t>
+          <t>-10.44%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.79%</t>
+          <t>10.87%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.69</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.45</v>
+        <v>39.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>177.23%</t>
+          <t>169.35%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.2</v>
+        <v>46.05</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.54%</t>
+          <t>43.07%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27.42%</t>
+          <t>25.92%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>159.91%</t>
+          <t>158.44%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>33.21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>111.35</v>
+        <v>111.85</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.92%</t>
+          <t>98.81%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>33.91</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>95.3</v>
+        <v>96</v>
       </c>
       <c r="D10" t="n">
-        <v>1.55</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.04%</t>
+          <t>98.48%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>32.16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.35</v>
+        <v>39.88</v>
       </c>
       <c r="D11" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>124.71%</t>
+          <t>127.74%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31.80</t>
+          <t>32.23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.47</v>
+        <v>16.52</v>
       </c>
       <c r="D12" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.70%</t>
+          <t>65.20%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>34.92</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H804"/>
+  <dimension ref="A1:H815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29213,10 +29213,8 @@
           <t>1.66%</t>
         </is>
       </c>
-      <c r="H794" t="inlineStr">
-        <is>
-          <t>23.86</t>
-        </is>
+      <c r="H794" t="n">
+        <v>23.86</v>
       </c>
     </row>
     <row r="795">
@@ -29251,11 +29249,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H795" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -29289,10 +29283,8 @@
           <t>10.79%</t>
         </is>
       </c>
-      <c r="H796" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
+      <c r="H796" t="n">
+        <v>37.95</v>
       </c>
     </row>
     <row r="797">
@@ -29327,10 +29319,8 @@
           <t>2.47%</t>
         </is>
       </c>
-      <c r="H797" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="H797" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="798">
@@ -29365,10 +29355,8 @@
           <t>3.03%</t>
         </is>
       </c>
-      <c r="H798" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
+      <c r="H798" t="n">
+        <v>21.79</v>
       </c>
     </row>
     <row r="799">
@@ -29403,10 +29391,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H799" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
+      <c r="H799" t="n">
+        <v>21.65</v>
       </c>
     </row>
     <row r="800">
@@ -29441,10 +29427,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H800" t="inlineStr">
-        <is>
-          <t>33.40</t>
-        </is>
+      <c r="H800" t="n">
+        <v>33.4</v>
       </c>
     </row>
     <row r="801">
@@ -29479,10 +29463,8 @@
           <t>1.44%</t>
         </is>
       </c>
-      <c r="H801" t="inlineStr">
-        <is>
-          <t>33.76</t>
-        </is>
+      <c r="H801" t="n">
+        <v>33.76</v>
       </c>
     </row>
     <row r="802">
@@ -29517,10 +29499,8 @@
           <t>3.36%</t>
         </is>
       </c>
-      <c r="H802" t="inlineStr">
-        <is>
-          <t>31.92</t>
-        </is>
+      <c r="H802" t="n">
+        <v>31.92</v>
       </c>
     </row>
     <row r="803">
@@ -29555,10 +29535,8 @@
           <t>10.04%</t>
         </is>
       </c>
-      <c r="H803" t="inlineStr">
-        <is>
-          <t>31.80</t>
-        </is>
+      <c r="H803" t="n">
+        <v>31.8</v>
       </c>
     </row>
     <row r="804">
@@ -29593,9 +29571,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H804" t="inlineStr">
-        <is>
-          <t>34.81</t>
+      <c r="H804" t="n">
+        <v>34.81</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>160</v>
+      </c>
+      <c r="D805" t="n">
+        <v>3</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>278.02%</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D806" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>13.80%</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D807" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>-10.44%</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>10.87%</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>37.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="D808" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>-2.84%</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>169.35%</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>22.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="D809" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>43.07%</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>3.04%</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>21.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D810" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>25.92%</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>21.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D811" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>158.44%</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>33.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>98.81%</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>33.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>96</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>98.48%</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>32.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>127.74%</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>9.90%</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>32.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>65.20%</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>34.92</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>160</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>278.02%</t>
+          <t>270.70%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.35</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.80%</t>
+          <t>14.61%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-10.44%</t>
+          <t>-12.83%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.87%</t>
+          <t>11.02%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.3</v>
+        <v>39.35</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.15</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>169.35%</t>
+          <t>171.49%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.05</v>
+        <v>45.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.07%</t>
+          <t>43.38%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>21.51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.92%</t>
+          <t>24.37%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>21.19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.6</v>
+        <v>17.75</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>158.44%</t>
+          <t>161.80%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>33.49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>111.85</v>
+        <v>112.45</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.81%</t>
+          <t>96.29%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.48%</t>
+          <t>96.98%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>32.29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,19 +825,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.88</v>
+        <v>39.89</v>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.74%</t>
+          <t>127.68%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -847,14 +847,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>32.24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.52</v>
+        <v>16.6</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.20%</t>
+          <t>66.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>35.09</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H815"/>
+  <dimension ref="A1:H826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29607,10 +29607,8 @@
           <t>1.63%</t>
         </is>
       </c>
-      <c r="H805" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
+      <c r="H805" t="n">
+        <v>24.28</v>
       </c>
     </row>
     <row r="806">
@@ -29645,11 +29643,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H806" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -29683,10 +29677,8 @@
           <t>10.87%</t>
         </is>
       </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>37.69</t>
-        </is>
+      <c r="H807" t="n">
+        <v>37.69</v>
       </c>
     </row>
     <row r="808">
@@ -29721,10 +29713,8 @@
           <t>2.54%</t>
         </is>
       </c>
-      <c r="H808" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
+      <c r="H808" t="n">
+        <v>22.59</v>
       </c>
     </row>
     <row r="809">
@@ -29759,10 +29749,8 @@
           <t>3.04%</t>
         </is>
       </c>
-      <c r="H809" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
+      <c r="H809" t="n">
+        <v>21.72</v>
       </c>
     </row>
     <row r="810">
@@ -29797,10 +29785,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H810" t="inlineStr">
-        <is>
-          <t>21.40</t>
-        </is>
+      <c r="H810" t="n">
+        <v>21.4</v>
       </c>
     </row>
     <row r="811">
@@ -29835,10 +29821,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H811" t="inlineStr">
-        <is>
-          <t>33.21</t>
-        </is>
+      <c r="H811" t="n">
+        <v>33.21</v>
       </c>
     </row>
     <row r="812">
@@ -29873,10 +29857,8 @@
           <t>1.43%</t>
         </is>
       </c>
-      <c r="H812" t="inlineStr">
-        <is>
-          <t>33.91</t>
-        </is>
+      <c r="H812" t="n">
+        <v>33.91</v>
       </c>
     </row>
     <row r="813">
@@ -29911,10 +29893,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H813" t="inlineStr">
-        <is>
-          <t>32.16</t>
-        </is>
+      <c r="H813" t="n">
+        <v>32.16</v>
       </c>
     </row>
     <row r="814">
@@ -29949,10 +29929,8 @@
           <t>9.90%</t>
         </is>
       </c>
-      <c r="H814" t="inlineStr">
-        <is>
-          <t>32.23</t>
-        </is>
+      <c r="H814" t="n">
+        <v>32.23</v>
       </c>
     </row>
     <row r="815">
@@ -29987,9 +29965,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>34.92</t>
+      <c r="H815" t="n">
+        <v>34.92</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>160</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>270.70%</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>14.61%</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>29</v>
+      </c>
+      <c r="D818" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>-12.83%</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>171.49%</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D820" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>43.38%</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>21.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>50</v>
+      </c>
+      <c r="D821" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>24.37%</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>21.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>161.80%</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>33.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="D823" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>96.29%</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>34.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="D824" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>96.98%</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>32.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="D825" t="n">
+        <v>0</v>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>127.68%</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>9.90%</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>32.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D826" t="n">
+        <v>0</v>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>66.00%</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>35.09</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>270.70%</t>
+          <t>249.24%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>23.37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14.61%</t>
+          <t>13.24%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.83%</t>
+          <t>-13.27%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.35</v>
+        <v>38.95</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-0.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>171.49%</t>
+          <t>168.73%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>45.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.38%</t>
+          <t>42.31%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.37%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.75</v>
+        <v>18.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>161.80%</t>
+          <t>167.99%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.49</t>
+          <t>34.43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.45</v>
+        <v>112.4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.29%</t>
+          <t>96.37%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>34.08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.40000000000001</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.98%</t>
+          <t>97.26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.29</t>
+          <t>32.28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.89</v>
+        <v>39.77</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.68%</t>
+          <t>129.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.93%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>32.14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.6</v>
+        <v>16.57</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.00%</t>
+          <t>65.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>35.02</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H826"/>
+  <dimension ref="A1:H837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30001,10 +30001,8 @@
           <t>1.63%</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
+      <c r="H816" t="n">
+        <v>24.28</v>
       </c>
     </row>
     <row r="817">
@@ -30039,11 +30037,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H817" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -30077,10 +30071,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H818" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H818" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="819">
@@ -30115,10 +30107,8 @@
           <t>2.54%</t>
         </is>
       </c>
-      <c r="H819" t="inlineStr">
-        <is>
-          <t>22.61</t>
-        </is>
+      <c r="H819" t="n">
+        <v>22.61</v>
       </c>
     </row>
     <row r="820">
@@ -30153,10 +30143,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H820" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
+      <c r="H820" t="n">
+        <v>21.51</v>
       </c>
     </row>
     <row r="821">
@@ -30191,10 +30179,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H821" t="inlineStr">
-        <is>
-          <t>21.19</t>
-        </is>
+      <c r="H821" t="n">
+        <v>21.19</v>
       </c>
     </row>
     <row r="822">
@@ -30229,10 +30215,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>33.49</t>
-        </is>
+      <c r="H822" t="n">
+        <v>33.49</v>
       </c>
     </row>
     <row r="823">
@@ -30267,10 +30251,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H823" t="inlineStr">
-        <is>
-          <t>34.09</t>
-        </is>
+      <c r="H823" t="n">
+        <v>34.09</v>
       </c>
     </row>
     <row r="824">
@@ -30305,10 +30287,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H824" t="inlineStr">
-        <is>
-          <t>32.29</t>
-        </is>
+      <c r="H824" t="n">
+        <v>32.29</v>
       </c>
     </row>
     <row r="825">
@@ -30343,10 +30323,8 @@
           <t>9.90%</t>
         </is>
       </c>
-      <c r="H825" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
+      <c r="H825" t="n">
+        <v>32.24</v>
       </c>
     </row>
     <row r="826">
@@ -30381,9 +30359,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H826" t="inlineStr">
-        <is>
-          <t>35.09</t>
+      <c r="H826" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>154</v>
+      </c>
+      <c r="D827" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>249.24%</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>23.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D828" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>13.24%</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>29</v>
+      </c>
+      <c r="D829" t="n">
+        <v>0</v>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>-13.27%</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D830" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>168.73%</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D831" t="n">
+        <v>0</v>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>42.31%</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>21.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D832" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>22.64%</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>21.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D833" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>167.99%</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D834" t="n">
+        <v>0</v>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>96.37%</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="D835" t="n">
+        <v>0</v>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>97.26%</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>32.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D836" t="n">
+        <v>0</v>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>129.06%</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>9.93%</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>32.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="D837" t="n">
+        <v>0</v>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>65.70%</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>35.02</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -748,25 +748,21 @@
           <t>台灣50(0050)</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>112.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.37%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -778,7 +774,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -786,25 +782,21 @@
           <t>ESG永續(00850)</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>96.34999999999999</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.26%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -816,7 +808,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -824,25 +816,21 @@
           <t>半導體收益(00927)</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.06%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -854,7 +842,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -862,20 +850,16 @@
           <t>凱基TOP50(009816)</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.70%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H837"/>
+  <dimension ref="A1:H848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30395,10 +30379,8 @@
           <t>1.69%</t>
         </is>
       </c>
-      <c r="H827" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="H827" t="n">
+        <v>23.37</v>
       </c>
     </row>
     <row r="828">
@@ -30433,11 +30415,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H828" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -30471,10 +30449,8 @@
           <t>11.02%</t>
         </is>
       </c>
-      <c r="H829" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H829" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="830">
@@ -30509,10 +30485,8 @@
           <t>2.57%</t>
         </is>
       </c>
-      <c r="H830" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
+      <c r="H830" t="n">
+        <v>22.39</v>
       </c>
     </row>
     <row r="831">
@@ -30547,10 +30521,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H831" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
+      <c r="H831" t="n">
+        <v>21.51</v>
       </c>
     </row>
     <row r="832">
@@ -30585,10 +30557,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H832" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
+      <c r="H832" t="n">
+        <v>21.02</v>
       </c>
     </row>
     <row r="833">
@@ -30623,10 +30593,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H833" t="inlineStr">
-        <is>
-          <t>34.43</t>
-        </is>
+      <c r="H833" t="n">
+        <v>34.43</v>
       </c>
     </row>
     <row r="834">
@@ -30661,10 +30629,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H834" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
+      <c r="H834" t="n">
+        <v>34.08</v>
       </c>
     </row>
     <row r="835">
@@ -30699,10 +30665,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H835" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="H835" t="n">
+        <v>32.28</v>
       </c>
     </row>
     <row r="836">
@@ -30737,10 +30701,8 @@
           <t>9.93%</t>
         </is>
       </c>
-      <c r="H836" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="H836" t="n">
+        <v>32.14</v>
       </c>
     </row>
     <row r="837">
@@ -30775,7 +30737,407 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H837" t="inlineStr">
+      <c r="H837" t="n">
+        <v>35.02</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>154</v>
+      </c>
+      <c r="D838" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>249.24%</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>23.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D839" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>13.24%</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>29</v>
+      </c>
+      <c r="D840" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>-13.27%</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D841" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>168.73%</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D842" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>42.31%</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>21.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D843" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>22.64%</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>21.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D844" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>167.99%</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr"/>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr"/>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>32.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr"/>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>32.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr"/>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
         <is>
           <t>35.02</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -748,21 +748,25 @@
           <t>台灣50(0050)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>96.37%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -774,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -782,21 +786,25 @@
           <t>ESG永續(00850)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>97.26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -808,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -816,21 +824,25 @@
           <t>半導體收益(00927)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.12</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>129.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>9.93%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -842,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -850,16 +862,20 @@
           <t>凱基TOP50(009816)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>65.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -884,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H848"/>
+  <dimension ref="A1:H859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30773,10 +30789,8 @@
           <t>1.69%</t>
         </is>
       </c>
-      <c r="H838" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="H838" t="n">
+        <v>23.37</v>
       </c>
     </row>
     <row r="839">
@@ -30811,11 +30825,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H839" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -30849,10 +30859,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H840" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H840" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="841">
@@ -30887,10 +30895,8 @@
           <t>2.57%</t>
         </is>
       </c>
-      <c r="H841" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
+      <c r="H841" t="n">
+        <v>22.39</v>
       </c>
     </row>
     <row r="842">
@@ -30925,10 +30931,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H842" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
+      <c r="H842" t="n">
+        <v>21.51</v>
       </c>
     </row>
     <row r="843">
@@ -30963,10 +30967,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H843" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
+      <c r="H843" t="n">
+        <v>21.02</v>
       </c>
     </row>
     <row r="844">
@@ -31001,10 +31003,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H844" t="inlineStr">
-        <is>
-          <t>34.43</t>
-        </is>
+      <c r="H844" t="n">
+        <v>34.43</v>
       </c>
     </row>
     <row r="845">
@@ -31035,10 +31035,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H845" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
+      <c r="H845" t="n">
+        <v>34.08</v>
       </c>
     </row>
     <row r="846">
@@ -31069,10 +31067,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H846" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="H846" t="n">
+        <v>32.28</v>
       </c>
     </row>
     <row r="847">
@@ -31103,10 +31099,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H847" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="H847" t="n">
+        <v>32.14</v>
       </c>
     </row>
     <row r="848">
@@ -31137,7 +31131,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H848" t="inlineStr">
+      <c r="H848" t="n">
+        <v>35.02</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>154</v>
+      </c>
+      <c r="D849" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>249.24%</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>23.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D850" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>13.24%</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>29</v>
+      </c>
+      <c r="D851" t="n">
+        <v>0</v>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>-13.27%</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D852" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>168.73%</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D853" t="n">
+        <v>0</v>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>42.31%</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>21.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D854" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>22.64%</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>21.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D855" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>167.99%</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D856" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>96.37%</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="D857" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>97.26%</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>32.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="D858" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>129.06%</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>9.93%</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>32.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="D859" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>65.70%</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
         <is>
           <t>35.02</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-6</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>249.24%</t>
+          <t>242.76%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>23.29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,16 +524,16 @@
         <v>20.1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.24%</t>
+          <t>15.19%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.27%</t>
+          <t>-18.44%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,16 +600,16 @@
         <v>38.95</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>168.73%</t>
+          <t>169.63%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.6</v>
+        <v>44.9</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.31%</t>
+          <t>40.34%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>21.18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.64%</t>
+          <t>19.84%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>20.81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.25</v>
+        <v>17.95</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>167.99%</t>
+          <t>160.90%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>33.87</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.4</v>
+        <v>111.3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>-1.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.37%</t>
+          <t>96.47%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>33.75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.34999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.85</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.26%</t>
+          <t>96.48%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>31.99</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.77</v>
+        <v>39.39</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.12</v>
+        <v>-0.38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.06%</t>
+          <t>129.78%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>10.03%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>31.83</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.57</v>
+        <v>16.4</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>-0.17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.70%</t>
+          <t>64.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>34.67</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H859"/>
+  <dimension ref="A1:H870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31167,10 +31167,8 @@
           <t>1.69%</t>
         </is>
       </c>
-      <c r="H849" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="H849" t="n">
+        <v>23.37</v>
       </c>
     </row>
     <row r="850">
@@ -31205,11 +31203,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H850" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -31243,10 +31237,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H851" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H851" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="852">
@@ -31281,10 +31273,8 @@
           <t>2.57%</t>
         </is>
       </c>
-      <c r="H852" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
+      <c r="H852" t="n">
+        <v>22.39</v>
       </c>
     </row>
     <row r="853">
@@ -31319,10 +31309,8 @@
           <t>3.07%</t>
         </is>
       </c>
-      <c r="H853" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
+      <c r="H853" t="n">
+        <v>21.51</v>
       </c>
     </row>
     <row r="854">
@@ -31357,10 +31345,8 @@
           <t>3.53%</t>
         </is>
       </c>
-      <c r="H854" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
+      <c r="H854" t="n">
+        <v>21.02</v>
       </c>
     </row>
     <row r="855">
@@ -31395,10 +31381,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H855" t="inlineStr">
-        <is>
-          <t>34.43</t>
-        </is>
+      <c r="H855" t="n">
+        <v>34.43</v>
       </c>
     </row>
     <row r="856">
@@ -31433,10 +31417,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H856" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
+      <c r="H856" t="n">
+        <v>34.08</v>
       </c>
     </row>
     <row r="857">
@@ -31471,10 +31453,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H857" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="H857" t="n">
+        <v>32.28</v>
       </c>
     </row>
     <row r="858">
@@ -31509,10 +31489,8 @@
           <t>9.93%</t>
         </is>
       </c>
-      <c r="H858" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="H858" t="n">
+        <v>32.14</v>
       </c>
     </row>
     <row r="859">
@@ -31547,9 +31525,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H859" t="inlineStr">
-        <is>
-          <t>35.02</t>
+      <c r="H859" t="n">
+        <v>35.02</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D860" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>242.76%</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>23.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D861" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>15.19%</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>29</v>
+      </c>
+      <c r="D862" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>-18.44%</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="D863" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>169.63%</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="D864" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>40.34%</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>21.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="D865" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>19.84%</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>20.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="D866" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>160.90%</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>33.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D867" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-0.98%</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>96.47%</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>33.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D868" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>96.48%</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>31.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="D869" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>129.78%</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>10.03%</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D870" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>64.00%</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>34.67</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>242.76%</t>
+          <t>244.99%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>24.37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.19%</t>
+          <t>18.05%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>29.65</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-18.44%</t>
+          <t>-16.62%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>38.01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.95</v>
+        <v>38.85</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>169.63%</t>
+          <t>168.94%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.9</v>
+        <v>44.85</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.34%</t>
+          <t>40.18%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>21.16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.1</v>
+        <v>49.15</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.84%</t>
+          <t>19.96%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>20.83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.95</v>
+        <v>19.7</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3</v>
+        <v>1.75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>160.90%</t>
+          <t>186.34%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>37.17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>111.3</v>
+        <v>112.05</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.47%</t>
+          <t>97.79%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>95.5</v>
+        <v>96.05</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.48%</t>
+          <t>97.61%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.39</v>
+        <v>39.89</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.78%</t>
+          <t>132.70%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.4</v>
+        <v>16.49</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.00%</t>
+          <t>64.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>34.86</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H870"/>
+  <dimension ref="A1:H881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31561,10 +31561,8 @@
           <t>1.70%</t>
         </is>
       </c>
-      <c r="H860" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
+      <c r="H860" t="n">
+        <v>23.29</v>
       </c>
     </row>
     <row r="861">
@@ -31582,7 +31580,7 @@
         <v>20.1</v>
       </c>
       <c r="D861" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E861" t="inlineStr">
         <is>
@@ -31599,11 +31597,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H861" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -31637,10 +31631,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H862" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H862" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="863">
@@ -31658,7 +31650,7 @@
         <v>38.95</v>
       </c>
       <c r="D863" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E863" t="inlineStr">
         <is>
@@ -31675,10 +31667,8 @@
           <t>2.57%</t>
         </is>
       </c>
-      <c r="H863" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
+      <c r="H863" t="n">
+        <v>22.39</v>
       </c>
     </row>
     <row r="864">
@@ -31713,10 +31703,8 @@
           <t>3.12%</t>
         </is>
       </c>
-      <c r="H864" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
+      <c r="H864" t="n">
+        <v>21.18</v>
       </c>
     </row>
     <row r="865">
@@ -31751,10 +31739,8 @@
           <t>3.56%</t>
         </is>
       </c>
-      <c r="H865" t="inlineStr">
-        <is>
-          <t>20.81</t>
-        </is>
+      <c r="H865" t="n">
+        <v>20.81</v>
       </c>
     </row>
     <row r="866">
@@ -31789,10 +31775,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H866" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
+      <c r="H866" t="n">
+        <v>33.87</v>
       </c>
     </row>
     <row r="867">
@@ -31827,10 +31811,8 @@
           <t>1.44%</t>
         </is>
       </c>
-      <c r="H867" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
+      <c r="H867" t="n">
+        <v>33.75</v>
       </c>
     </row>
     <row r="868">
@@ -31865,10 +31847,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H868" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
+      <c r="H868" t="n">
+        <v>31.99</v>
       </c>
     </row>
     <row r="869">
@@ -31903,10 +31883,8 @@
           <t>10.03%</t>
         </is>
       </c>
-      <c r="H869" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
+      <c r="H869" t="n">
+        <v>31.83</v>
       </c>
     </row>
     <row r="870">
@@ -31941,9 +31919,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H870" t="inlineStr">
-        <is>
-          <t>34.67</t>
+      <c r="H870" t="n">
+        <v>34.67</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="D871" t="n">
+        <v>1</v>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>244.99%</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>24.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D872" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>18.05%</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="D873" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>-16.62%</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>38.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="D874" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>168.94%</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>22.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="D875" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>40.18%</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>21.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="D876" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>19.96%</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D877" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>9.75%</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>186.34%</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>37.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="D878" t="n">
+        <v>0</v>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>97.79%</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>33.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>96.05</v>
+      </c>
+      <c r="D879" t="n">
+        <v>0</v>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>97.61%</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="D880" t="n">
+        <v>0</v>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>132.70%</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>9.90%</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>32.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="D881" t="n">
+        <v>0</v>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>64.90%</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>34.86</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>154.5</v>
+        <v>161.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>4.53%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>244.99%</t>
+          <t>271.22%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>20.15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.05%</t>
+          <t>16.14%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.65</v>
+        <v>29.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.65</v>
+        <v>-0.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.62%</t>
+          <t>-18.16%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>37.31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.85</v>
+        <v>36.9</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1</v>
+        <v>-1.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>168.94%</t>
+          <t>156.30%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>21.21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.85</v>
+        <v>45.35</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.18%</t>
+          <t>41.74%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.15</v>
+        <v>48.85</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.96%</t>
+          <t>19.79%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.75</v>
+        <v>-1.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9.75%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>186.34%</t>
+          <t>174.48%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>37.17</t>
+          <t>34.91</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.05</v>
+        <v>112.9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.79%</t>
+          <t>98.26%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>34.23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.05</v>
+        <v>96.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.61%</t>
+          <t>98.15%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>32.33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.89</v>
+        <v>40.29</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>132.70%</t>
+          <t>136.61%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.80%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>32.56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.49</v>
+        <v>16.6</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.90%</t>
+          <t>66.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>35.09</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H881"/>
+  <dimension ref="A1:H892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31955,10 +31955,8 @@
           <t>1.69%</t>
         </is>
       </c>
-      <c r="H871" t="inlineStr">
-        <is>
-          <t>24.37</t>
-        </is>
+      <c r="H871" t="n">
+        <v>24.37</v>
       </c>
     </row>
     <row r="872">
@@ -31993,11 +31991,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H872" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -32031,10 +32025,8 @@
           <t>3.37%</t>
         </is>
       </c>
-      <c r="H873" t="inlineStr">
-        <is>
-          <t>38.01</t>
-        </is>
+      <c r="H873" t="n">
+        <v>38.01</v>
       </c>
     </row>
     <row r="874">
@@ -32069,10 +32061,8 @@
           <t>2.57%</t>
         </is>
       </c>
-      <c r="H874" t="inlineStr">
-        <is>
-          <t>22.33</t>
-        </is>
+      <c r="H874" t="n">
+        <v>22.33</v>
       </c>
     </row>
     <row r="875">
@@ -32107,10 +32097,8 @@
           <t>3.12%</t>
         </is>
       </c>
-      <c r="H875" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
+      <c r="H875" t="n">
+        <v>21.16</v>
       </c>
     </row>
     <row r="876">
@@ -32145,10 +32133,8 @@
           <t>3.56%</t>
         </is>
       </c>
-      <c r="H876" t="inlineStr">
-        <is>
-          <t>20.83</t>
-        </is>
+      <c r="H876" t="n">
+        <v>20.83</v>
       </c>
     </row>
     <row r="877">
@@ -32183,10 +32169,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H877" t="inlineStr">
-        <is>
-          <t>37.17</t>
-        </is>
+      <c r="H877" t="n">
+        <v>37.17</v>
       </c>
     </row>
     <row r="878">
@@ -32221,10 +32205,8 @@
           <t>1.43%</t>
         </is>
       </c>
-      <c r="H878" t="inlineStr">
-        <is>
-          <t>33.97</t>
-        </is>
+      <c r="H878" t="n">
+        <v>33.97</v>
       </c>
     </row>
     <row r="879">
@@ -32259,10 +32241,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H879" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
+      <c r="H879" t="n">
+        <v>32.18</v>
       </c>
     </row>
     <row r="880">
@@ -32297,10 +32277,8 @@
           <t>9.90%</t>
         </is>
       </c>
-      <c r="H880" t="inlineStr">
-        <is>
-          <t>32.24</t>
-        </is>
+      <c r="H880" t="n">
+        <v>32.24</v>
       </c>
     </row>
     <row r="881">
@@ -32335,9 +32313,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H881" t="inlineStr">
-        <is>
-          <t>34.86</t>
+      <c r="H881" t="n">
+        <v>34.86</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D882" t="n">
+        <v>7</v>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>4.53%</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>271.22%</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>24.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D883" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>-2.18%</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>16.14%</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D884" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>-1.85%</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>-18.16%</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>37.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="D885" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>-5.02%</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>156.30%</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>21.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="D886" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>41.74%</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>21.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="D887" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>-0.61%</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>19.79%</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D888" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>-6.09%</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>174.48%</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>34.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="D889" t="n">
+        <v>0</v>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>98.26%</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>34.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="D890" t="n">
+        <v>0</v>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>98.15%</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>32.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="D891" t="n">
+        <v>0</v>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>136.61%</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>9.80%</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>32.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D892" t="n">
+        <v>0</v>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>66.00%</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>35.09</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>161.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.53%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>271.22%</t>
+          <t>275.03%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.15</v>
+        <v>20.45</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.14%</t>
+          <t>17.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-18.16%</t>
+          <t>-17.88%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>37.44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.9</v>
+        <v>37.35</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.95</v>
+        <v>0.45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>156.30%</t>
+          <t>156.83%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>45.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.74%</t>
+          <t>43.25%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>48.85</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.79%</t>
+          <t>20.50%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.5</v>
+        <v>19.35</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2</v>
+        <v>0.85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-6.09%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>174.48%</t>
+          <t>191.86%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>36.51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.9</v>
+        <v>112.8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.26%</t>
+          <t>94.41%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>34.20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>98.15%</t>
+          <t>96.06%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.33</t>
+          <t>32.39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.29</v>
+        <v>40.52</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>136.61%</t>
+          <t>134.69%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.80%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.6</v>
+        <v>16.58</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.00%</t>
+          <t>65.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>35.05</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H892"/>
+  <dimension ref="A1:H903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32349,10 +32349,8 @@
           <t>1.61%</t>
         </is>
       </c>
-      <c r="H882" t="inlineStr">
-        <is>
-          <t>24.47</t>
-        </is>
+      <c r="H882" t="n">
+        <v>24.47</v>
       </c>
     </row>
     <row r="883">
@@ -32387,11 +32385,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H883" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -32425,10 +32419,8 @@
           <t>3.44%</t>
         </is>
       </c>
-      <c r="H884" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="H884" t="n">
+        <v>37.31</v>
       </c>
     </row>
     <row r="885">
@@ -32463,10 +32455,8 @@
           <t>2.71%</t>
         </is>
       </c>
-      <c r="H885" t="inlineStr">
-        <is>
-          <t>21.21</t>
-        </is>
+      <c r="H885" t="n">
+        <v>21.21</v>
       </c>
     </row>
     <row r="886">
@@ -32501,10 +32491,8 @@
           <t>3.09%</t>
         </is>
       </c>
-      <c r="H886" t="inlineStr">
-        <is>
-          <t>21.39</t>
-        </is>
+      <c r="H886" t="n">
+        <v>21.39</v>
       </c>
     </row>
     <row r="887">
@@ -32539,10 +32527,8 @@
           <t>3.58%</t>
         </is>
       </c>
-      <c r="H887" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
+      <c r="H887" t="n">
+        <v>20.7</v>
       </c>
     </row>
     <row r="888">
@@ -32577,10 +32563,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H888" t="inlineStr">
-        <is>
-          <t>34.91</t>
-        </is>
+      <c r="H888" t="n">
+        <v>34.91</v>
       </c>
     </row>
     <row r="889">
@@ -32615,10 +32599,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H889" t="inlineStr">
-        <is>
-          <t>34.23</t>
-        </is>
+      <c r="H889" t="n">
+        <v>34.23</v>
       </c>
     </row>
     <row r="890">
@@ -32653,10 +32635,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H890" t="inlineStr">
-        <is>
-          <t>32.33</t>
-        </is>
+      <c r="H890" t="n">
+        <v>32.33</v>
       </c>
     </row>
     <row r="891">
@@ -32691,10 +32671,8 @@
           <t>9.80%</t>
         </is>
       </c>
-      <c r="H891" t="inlineStr">
-        <is>
-          <t>32.56</t>
-        </is>
+      <c r="H891" t="n">
+        <v>32.56</v>
       </c>
     </row>
     <row r="892">
@@ -32729,9 +32707,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H892" t="inlineStr">
-        <is>
-          <t>35.09</t>
+      <c r="H892" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D893" t="n">
+        <v>0</v>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>275.03%</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>24.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="D894" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>17.53%</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D895" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>-17.88%</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>37.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="D896" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>156.83%</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>21.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="D897" t="n">
+        <v>0</v>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>43.25%</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>21.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="D898" t="n">
+        <v>0</v>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>20.50%</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="D899" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>191.86%</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>36.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="D900" t="n">
+        <v>0</v>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>94.41%</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>34.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="D901" t="n">
+        <v>0</v>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>96.06%</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>32.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="D902" t="n">
+        <v>0</v>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>134.69%</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>9.75%</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="D903" t="n">
+        <v>0</v>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>65.80%</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>35.05</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>161.5</v>
+        <v>152.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-5.57%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>275.03%</t>
+          <t>250.14%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>23.14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.45</v>
+        <v>20.15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.53%</t>
+          <t>12.26%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.2</v>
+        <v>28.95</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.88%</t>
+          <t>-15.44%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.35</v>
+        <v>37.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>156.83%</t>
+          <t>159.07%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.35</v>
+        <v>44.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.25%</t>
+          <t>42.81%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>21.13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.85</v>
+        <v>48.55</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.50%</t>
+          <t>20.33%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>20.57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.35</v>
+        <v>18.85</v>
       </c>
       <c r="D8" t="n">
-        <v>0.85</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>191.86%</t>
+          <t>185.17%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>34.91</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.8</v>
+        <v>115.95</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94.41%</t>
+          <t>91.74%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.20</t>
+          <t>35.15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.7</v>
+        <v>99.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.06%</t>
+          <t>94.53%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>33.23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.52</v>
+        <v>40.82</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>134.69%</t>
+          <t>128.96%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.75%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>32.99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.58</v>
+        <v>16.99</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.80%</t>
+          <t>69.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>35.91</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H903"/>
+  <dimension ref="A1:H914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32743,10 +32743,8 @@
           <t>1.61%</t>
         </is>
       </c>
-      <c r="H893" t="inlineStr">
-        <is>
-          <t>24.47</t>
-        </is>
+      <c r="H893" t="n">
+        <v>24.47</v>
       </c>
     </row>
     <row r="894">
@@ -32781,11 +32779,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H894" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -32819,10 +32813,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H895" t="inlineStr">
-        <is>
-          <t>37.44</t>
-        </is>
+      <c r="H895" t="n">
+        <v>37.44</v>
       </c>
     </row>
     <row r="896">
@@ -32857,10 +32849,8 @@
           <t>2.68%</t>
         </is>
       </c>
-      <c r="H896" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
+      <c r="H896" t="n">
+        <v>21.47</v>
       </c>
     </row>
     <row r="897">
@@ -32895,10 +32885,8 @@
           <t>3.09%</t>
         </is>
       </c>
-      <c r="H897" t="inlineStr">
-        <is>
-          <t>21.39</t>
-        </is>
+      <c r="H897" t="n">
+        <v>21.39</v>
       </c>
     </row>
     <row r="898">
@@ -32933,10 +32921,8 @@
           <t>3.58%</t>
         </is>
       </c>
-      <c r="H898" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
+      <c r="H898" t="n">
+        <v>20.7</v>
       </c>
     </row>
     <row r="899">
@@ -32971,10 +32957,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H899" t="inlineStr">
-        <is>
-          <t>36.51</t>
-        </is>
+      <c r="H899" t="n">
+        <v>36.51</v>
       </c>
     </row>
     <row r="900">
@@ -33009,10 +32993,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H900" t="inlineStr">
-        <is>
-          <t>34.20</t>
-        </is>
+      <c r="H900" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="901">
@@ -33047,10 +33029,8 @@
           <t>3.31%</t>
         </is>
       </c>
-      <c r="H901" t="inlineStr">
-        <is>
-          <t>32.39</t>
-        </is>
+      <c r="H901" t="n">
+        <v>32.39</v>
       </c>
     </row>
     <row r="902">
@@ -33085,10 +33065,8 @@
           <t>9.75%</t>
         </is>
       </c>
-      <c r="H902" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="H902" t="n">
+        <v>32.74</v>
       </c>
     </row>
     <row r="903">
@@ -33123,9 +33101,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H903" t="inlineStr">
-        <is>
-          <t>35.05</t>
+      <c r="H903" t="n">
+        <v>35.05</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="D904" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>-5.57%</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>250.14%</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>23.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D905" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>12.26%</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="D906" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>-15.44%</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>37.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D907" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>159.07%</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>21.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D908" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>42.81%</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>21.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="D909" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>-0.61%</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>20.33%</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>20.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D910" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>185.17%</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>34.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="D911" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>91.74%</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>35.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="D912" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2.59%</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>94.53%</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>33.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="D913" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>128.96%</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>9.68%</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>32.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="D914" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>2.47%</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>69.90%</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>35.91</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>250.14%</t>
+          <t>238.66%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>22.38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.15</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.26%</t>
+          <t>13.65%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.95</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.44%</t>
+          <t>-15.88%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>36.92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.3</v>
+        <v>37.65</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>159.07%</t>
+          <t>161.50%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.8</v>
+        <v>45.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.55</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.81%</t>
+          <t>44.88%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>21.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48.55</v>
+        <v>49.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.33%</t>
+          <t>22.19%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.89</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.85</v>
+        <v>18.4</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.17%</t>
+          <t>178.37%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>34.07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>115.95</v>
+        <v>116.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.15</v>
+        <v>0.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.74%</t>
+          <t>92.65%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>35.32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.53%</t>
+          <t>94.92%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>33.30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.82</v>
+        <v>40.72</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.96%</t>
+          <t>128.40%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>9.70%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>32.91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.99</v>
+        <v>17.06</v>
       </c>
       <c r="D12" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.90%</t>
+          <t>70.60%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>36.06</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H914"/>
+  <dimension ref="A1:H925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33137,10 +33137,8 @@
           <t>1.71%</t>
         </is>
       </c>
-      <c r="H904" t="inlineStr">
-        <is>
-          <t>23.14</t>
-        </is>
+      <c r="H904" t="n">
+        <v>23.14</v>
       </c>
     </row>
     <row r="905">
@@ -33175,11 +33173,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H905" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -33213,10 +33207,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H906" t="inlineStr">
-        <is>
-          <t>37.12</t>
-        </is>
+      <c r="H906" t="n">
+        <v>37.12</v>
       </c>
     </row>
     <row r="907">
@@ -33251,10 +33243,8 @@
           <t>2.68%</t>
         </is>
       </c>
-      <c r="H907" t="inlineStr">
-        <is>
-          <t>21.44</t>
-        </is>
+      <c r="H907" t="n">
+        <v>21.44</v>
       </c>
     </row>
     <row r="908">
@@ -33289,10 +33279,8 @@
           <t>3.12%</t>
         </is>
       </c>
-      <c r="H908" t="inlineStr">
-        <is>
-          <t>21.13</t>
-        </is>
+      <c r="H908" t="n">
+        <v>21.13</v>
       </c>
     </row>
     <row r="909">
@@ -33327,10 +33315,8 @@
           <t>3.60%</t>
         </is>
       </c>
-      <c r="H909" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
+      <c r="H909" t="n">
+        <v>20.57</v>
       </c>
     </row>
     <row r="910">
@@ -33365,10 +33351,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H910" t="inlineStr">
-        <is>
-          <t>34.91</t>
-        </is>
+      <c r="H910" t="n">
+        <v>34.91</v>
       </c>
     </row>
     <row r="911">
@@ -33403,10 +33387,8 @@
           <t>1.38%</t>
         </is>
       </c>
-      <c r="H911" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
+      <c r="H911" t="n">
+        <v>35.15</v>
       </c>
     </row>
     <row r="912">
@@ -33441,10 +33423,8 @@
           <t>3.23%</t>
         </is>
       </c>
-      <c r="H912" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="H912" t="n">
+        <v>33.23</v>
       </c>
     </row>
     <row r="913">
@@ -33479,10 +33459,8 @@
           <t>9.68%</t>
         </is>
       </c>
-      <c r="H913" t="inlineStr">
-        <is>
-          <t>32.99</t>
-        </is>
+      <c r="H913" t="n">
+        <v>32.99</v>
       </c>
     </row>
     <row r="914">
@@ -33517,9 +33495,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H914" t="inlineStr">
-        <is>
-          <t>35.91</t>
+      <c r="H914" t="n">
+        <v>35.91</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D915" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>238.66%</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>22.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>13.65%</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D917" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>-15.88%</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>36.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>161.50%</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>44.88%</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>3.08%</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D920" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>22.19%</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>20.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D921" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>178.37%</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>34.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="D922" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>92.65%</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>35.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D923" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>94.92%</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>33.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="D924" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>128.40%</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>9.70%</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>32.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="D925" t="n">
+        <v>0</v>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>70.60%</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>36.06</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>147.5</v>
+        <v>148.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>238.66%</t>
+          <t>240.95%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.65%</t>
+          <t>17.55%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.88%</t>
+          <t>-15.58%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>37.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.65</v>
+        <v>38.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.35</v>
+        <v>0.85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>161.50%</t>
+          <t>167.41%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>22.13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.45</v>
+        <v>45.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.88%</t>
+          <t>45.83%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.19%</t>
+          <t>23.43%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>178.37%</t>
+          <t>181.39%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116.5</v>
+        <v>116.05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.65%</t>
+          <t>91.90%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.92%</t>
+          <t>94.14%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>33.30</t>
+          <t>33.16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.72</v>
+        <v>40.52</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.40%</t>
+          <t>127.28%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.06</v>
+        <v>17.04</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.60%</t>
+          <t>70.40%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.02</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H925"/>
+  <dimension ref="A1:H936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33531,10 +33531,8 @@
           <t>1.77%</t>
         </is>
       </c>
-      <c r="H915" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
+      <c r="H915" t="n">
+        <v>22.38</v>
       </c>
     </row>
     <row r="916">
@@ -33569,11 +33567,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H916" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -33607,10 +33601,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H917" t="inlineStr">
-        <is>
-          <t>36.92</t>
-        </is>
+      <c r="H917" t="n">
+        <v>36.92</v>
       </c>
     </row>
     <row r="918">
@@ -33645,10 +33637,8 @@
           <t>2.66%</t>
         </is>
       </c>
-      <c r="H918" t="inlineStr">
-        <is>
-          <t>21.64</t>
-        </is>
+      <c r="H918" t="n">
+        <v>21.64</v>
       </c>
     </row>
     <row r="919">
@@ -33683,10 +33673,8 @@
           <t>3.08%</t>
         </is>
       </c>
-      <c r="H919" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="H919" t="n">
+        <v>21.75</v>
       </c>
     </row>
     <row r="920">
@@ -33721,10 +33709,8 @@
           <t>3.55%</t>
         </is>
       </c>
-      <c r="H920" t="inlineStr">
-        <is>
-          <t>20.89</t>
-        </is>
+      <c r="H920" t="n">
+        <v>20.89</v>
       </c>
     </row>
     <row r="921">
@@ -33759,10 +33745,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H921" t="inlineStr">
-        <is>
-          <t>34.07</t>
-        </is>
+      <c r="H921" t="n">
+        <v>34.07</v>
       </c>
     </row>
     <row r="922">
@@ -33797,10 +33781,8 @@
           <t>1.37%</t>
         </is>
       </c>
-      <c r="H922" t="inlineStr">
-        <is>
-          <t>35.32</t>
-        </is>
+      <c r="H922" t="n">
+        <v>35.32</v>
       </c>
     </row>
     <row r="923">
@@ -33835,10 +33817,8 @@
           <t>3.22%</t>
         </is>
       </c>
-      <c r="H923" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
+      <c r="H923" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="924">
@@ -33873,10 +33853,8 @@
           <t>9.70%</t>
         </is>
       </c>
-      <c r="H924" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
+      <c r="H924" t="n">
+        <v>32.91</v>
       </c>
     </row>
     <row r="925">
@@ -33911,9 +33889,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H925" t="inlineStr">
-        <is>
-          <t>36.06</t>
+      <c r="H925" t="n">
+        <v>36.06</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="D926" t="n">
+        <v>1</v>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>240.95%</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>22.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D927" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>17.55%</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D928" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>-15.58%</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>37.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D929" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>167.41%</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>22.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="D930" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>45.83%</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>3.06%</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>21.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="D931" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>23.43%</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>21.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D932" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>181.39%</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>34.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="D933" t="n">
+        <v>0</v>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>91.90%</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>35.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>99</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0</v>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>94.14%</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>33.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="D935" t="n">
+        <v>0</v>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>127.28%</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>9.75%</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>70.40%</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>36.02</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>240.95%</t>
+          <t>233.76%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>22.38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.55%</t>
+          <t>16.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.9</v>
+        <v>28.55</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-15.58%</t>
+          <t>-13.43%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.5</v>
+        <v>37.55</v>
       </c>
       <c r="D5" t="n">
-        <v>0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>167.41%</t>
+          <t>159.07%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.75</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>-0.75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.83%</t>
+          <t>43.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.43%</t>
+          <t>21.90%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>20.89</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.6</v>
+        <v>18.15</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>181.39%</t>
+          <t>173.34%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>33.61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116.05</v>
+        <v>114.95</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.90%</t>
+          <t>91.79%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.85</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>99</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.14%</t>
+          <t>93.82%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>32.86</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.52</v>
+        <v>40.27</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.28%</t>
+          <t>125.88%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.75%</t>
+          <t>9.81%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>32.54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.04</v>
+        <v>16.87</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.40%</t>
+          <t>68.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>35.66</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H936"/>
+  <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33925,10 +33925,8 @@
           <t>1.76%</t>
         </is>
       </c>
-      <c r="H926" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
+      <c r="H926" t="n">
+        <v>22.53</v>
       </c>
     </row>
     <row r="927">
@@ -33963,11 +33961,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H927" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H927" t="inlineStr"/>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -34001,10 +33995,8 @@
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H928" t="inlineStr">
-        <is>
-          <t>37.05</t>
-        </is>
+      <c r="H928" t="n">
+        <v>37.05</v>
       </c>
     </row>
     <row r="929">
@@ -34039,10 +34031,8 @@
           <t>2.60%</t>
         </is>
       </c>
-      <c r="H929" t="inlineStr">
-        <is>
-          <t>22.13</t>
-        </is>
+      <c r="H929" t="n">
+        <v>22.13</v>
       </c>
     </row>
     <row r="930">
@@ -34077,10 +34067,8 @@
           <t>3.06%</t>
         </is>
       </c>
-      <c r="H930" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
+      <c r="H930" t="n">
+        <v>21.58</v>
       </c>
     </row>
     <row r="931">
@@ -34115,10 +34103,8 @@
           <t>3.51%</t>
         </is>
       </c>
-      <c r="H931" t="inlineStr">
-        <is>
-          <t>21.10</t>
-        </is>
+      <c r="H931" t="n">
+        <v>21.1</v>
       </c>
     </row>
     <row r="932">
@@ -34153,10 +34139,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H932" t="inlineStr">
-        <is>
-          <t>34.44</t>
-        </is>
+      <c r="H932" t="n">
+        <v>34.44</v>
       </c>
     </row>
     <row r="933">
@@ -34191,10 +34175,8 @@
           <t>1.38%</t>
         </is>
       </c>
-      <c r="H933" t="inlineStr">
-        <is>
-          <t>35.19</t>
-        </is>
+      <c r="H933" t="n">
+        <v>35.19</v>
       </c>
     </row>
     <row r="934">
@@ -34229,10 +34211,8 @@
           <t>3.23%</t>
         </is>
       </c>
-      <c r="H934" t="inlineStr">
-        <is>
-          <t>33.16</t>
-        </is>
+      <c r="H934" t="n">
+        <v>33.16</v>
       </c>
     </row>
     <row r="935">
@@ -34267,10 +34247,8 @@
           <t>9.75%</t>
         </is>
       </c>
-      <c r="H935" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="H935" t="n">
+        <v>32.74</v>
       </c>
     </row>
     <row r="936">
@@ -34305,9 +34283,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H936" t="inlineStr">
-        <is>
-          <t>36.02</t>
+      <c r="H936" t="n">
+        <v>36.02</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D937" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>233.76%</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>22.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D938" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>16.53%</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="D939" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>-13.43%</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>36.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D940" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>-2.47%</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>159.07%</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>21.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>45</v>
+      </c>
+      <c r="D941" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>43.01%</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>21.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D942" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>21.90%</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>20.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D943" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>-2.42%</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>173.34%</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>33.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0</v>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>91.79%</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="D945" t="n">
+        <v>0</v>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>93.82%</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>32.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="D946" t="n">
+        <v>0</v>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>125.88%</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>9.81%</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>32.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="D947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>68.70%</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>35.66</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -748,25 +748,21 @@
           <t>台灣50(0050)</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>114.95</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.79%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -778,7 +774,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -786,25 +782,21 @@
           <t>ESG永續(00850)</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93.82%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -816,7 +808,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -824,25 +816,21 @@
           <t>半導體收益(00927)</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>40.27</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>125.88%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -854,7 +842,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -862,20 +850,16 @@
           <t>凱基TOP50(009816)</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68.70%</t>
+          <t>nan%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -900,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H947"/>
+  <dimension ref="A1:H958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34319,10 +34303,8 @@
           <t>1.77%</t>
         </is>
       </c>
-      <c r="H937" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
+      <c r="H937" t="n">
+        <v>22.38</v>
       </c>
     </row>
     <row r="938">
@@ -34357,11 +34339,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H938" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H938" t="inlineStr"/>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -34395,10 +34373,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H939" t="inlineStr">
-        <is>
-          <t>36.60</t>
-        </is>
+      <c r="H939" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="940">
@@ -34433,10 +34409,8 @@
           <t>2.66%</t>
         </is>
       </c>
-      <c r="H940" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
+      <c r="H940" t="n">
+        <v>21.58</v>
       </c>
     </row>
     <row r="941">
@@ -34471,10 +34445,8 @@
           <t>3.11%</t>
         </is>
       </c>
-      <c r="H941" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
+      <c r="H941" t="n">
+        <v>21.53</v>
       </c>
     </row>
     <row r="942">
@@ -34509,10 +34481,8 @@
           <t>3.55%</t>
         </is>
       </c>
-      <c r="H942" t="inlineStr">
-        <is>
-          <t>20.89</t>
-        </is>
+      <c r="H942" t="n">
+        <v>20.89</v>
       </c>
     </row>
     <row r="943">
@@ -34547,10 +34517,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H943" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
+      <c r="H943" t="n">
+        <v>33.61</v>
       </c>
     </row>
     <row r="944">
@@ -34585,10 +34553,8 @@
           <t>1.39%</t>
         </is>
       </c>
-      <c r="H944" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
+      <c r="H944" t="n">
+        <v>34.85</v>
       </c>
     </row>
     <row r="945">
@@ -34623,10 +34589,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H945" t="inlineStr">
-        <is>
-          <t>32.86</t>
-        </is>
+      <c r="H945" t="n">
+        <v>32.86</v>
       </c>
     </row>
     <row r="946">
@@ -34661,10 +34625,8 @@
           <t>9.81%</t>
         </is>
       </c>
-      <c r="H946" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="H946" t="n">
+        <v>32.54</v>
       </c>
     </row>
     <row r="947">
@@ -34699,7 +34661,407 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H947" t="inlineStr">
+      <c r="H947" t="n">
+        <v>35.66</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D948" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>233.76%</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>22.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D949" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>-1.42%</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>16.53%</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="D950" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>-13.43%</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>36.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="D951" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>-2.47%</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>159.07%</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>21.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>45</v>
+      </c>
+      <c r="D952" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>43.01%</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>3.11%</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>21.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="D953" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>21.90%</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>20.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D954" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>-2.42%</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>173.34%</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>33.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr"/>
+      <c r="D955" t="inlineStr"/>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr"/>
+      <c r="D956" t="inlineStr"/>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>32.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr"/>
+      <c r="D957" t="inlineStr"/>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>32.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr"/>
+      <c r="D958" t="inlineStr"/>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
         <is>
           <t>35.66</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>147.5</v>
+        <v>145.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>233.76%</t>
+          <t>225.61%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.53%</t>
+          <t>18.41%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.55</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.35</v>
+        <v>0.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.43%</t>
+          <t>-5.11%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.60</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.55</v>
+        <v>38.8</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.95</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>159.07%</t>
+          <t>165.92%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>22.30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.75</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.01%</t>
+          <t>47.53%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.70</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.90%</t>
+          <t>24.52%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>18.15</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173.34%</t>
+          <t>185.38%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -748,33 +748,37 @@
           <t>台灣50(0050)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>92.01%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>34.81</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -782,33 +786,37 @@
           <t>ESG永續(00850)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>95.52%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>32.96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -816,33 +824,37 @@
           <t>半導體收益(00927)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.11</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>129.21%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>9.78%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>32.63</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -850,16 +862,20 @@
           <t>凱基TOP50(009816)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>68.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -869,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>35.70</t>
         </is>
       </c>
     </row>
@@ -884,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H958"/>
+  <dimension ref="A1:H969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34697,10 +34713,8 @@
           <t>1.77%</t>
         </is>
       </c>
-      <c r="H948" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
+      <c r="H948" t="n">
+        <v>22.38</v>
       </c>
     </row>
     <row r="949">
@@ -34735,11 +34749,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H949" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H949" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -34773,10 +34783,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H950" t="inlineStr">
-        <is>
-          <t>36.60</t>
-        </is>
+      <c r="H950" t="n">
+        <v>36.6</v>
       </c>
     </row>
     <row r="951">
@@ -34811,10 +34819,8 @@
           <t>2.66%</t>
         </is>
       </c>
-      <c r="H951" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
+      <c r="H951" t="n">
+        <v>21.58</v>
       </c>
     </row>
     <row r="952">
@@ -34849,10 +34855,8 @@
           <t>3.11%</t>
         </is>
       </c>
-      <c r="H952" t="inlineStr">
-        <is>
-          <t>21.23</t>
-        </is>
+      <c r="H952" t="n">
+        <v>21.23</v>
       </c>
     </row>
     <row r="953">
@@ -34887,10 +34891,8 @@
           <t>3.55%</t>
         </is>
       </c>
-      <c r="H953" t="inlineStr">
-        <is>
-          <t>20.89</t>
-        </is>
+      <c r="H953" t="n">
+        <v>20.89</v>
       </c>
     </row>
     <row r="954">
@@ -34925,10 +34927,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H954" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
+      <c r="H954" t="n">
+        <v>33.61</v>
       </c>
     </row>
     <row r="955">
@@ -34959,10 +34959,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H955" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
+      <c r="H955" t="n">
+        <v>34.85</v>
       </c>
     </row>
     <row r="956">
@@ -34993,10 +34991,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H956" t="inlineStr">
-        <is>
-          <t>32.86</t>
-        </is>
+      <c r="H956" t="n">
+        <v>32.86</v>
       </c>
     </row>
     <row r="957">
@@ -35027,10 +35023,8 @@
           <t>nan%</t>
         </is>
       </c>
-      <c r="H957" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="H957" t="n">
+        <v>32.54</v>
       </c>
     </row>
     <row r="958">
@@ -35061,9 +35055,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H958" t="inlineStr">
-        <is>
-          <t>35.66</t>
+      <c r="H958" t="n">
+        <v>35.66</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D959" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>225.61%</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>22.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D960" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>18.41%</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>29</v>
+      </c>
+      <c r="D961" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>-5.11%</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D962" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>165.92%</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>22.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>46</v>
+      </c>
+      <c r="D963" t="n">
+        <v>1</v>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>47.53%</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>3.04%</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>50</v>
+      </c>
+      <c r="D964" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>24.52%</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>21.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>185.38%</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>33.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="D966" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>92.01%</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>34.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D967" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>95.52%</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>32.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="D968" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>129.21%</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>9.78%</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>32.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="D969" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>68.90%</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>35.70</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145.5</v>
+        <v>141.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>225.61%</t>
+          <t>216.66%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>21.47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.9</v>
+        <v>20.35</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.41%</t>
+          <t>15.30%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.95</v>
       </c>
       <c r="D4" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-5.27%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -581,14 +581,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>37.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.8</v>
+        <v>38.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>165.92%</t>
+          <t>165.58%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>22.27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.53%</t>
+          <t>49.14%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>22.46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.52%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>21.85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.15</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.38%</t>
+          <t>179.87%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>32.96</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>114.8</v>
+        <v>112.4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.15</v>
+        <v>-2.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.01%</t>
+          <t>88.00%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>34.08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>98.40000000000001</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>-2.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.52%</t>
+          <t>91.45%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>32.28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40.38</v>
+        <v>39.63</v>
       </c>
       <c r="D11" t="n">
-        <v>0.11</v>
+        <v>-0.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.21%</t>
+          <t>124.95%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.78%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.89</v>
+        <v>16.61</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68.90%</t>
+          <t>66.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.70</t>
+          <t>35.11</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H969"/>
+  <dimension ref="A1:H980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35091,10 +35091,8 @@
           <t>1.79%</t>
         </is>
       </c>
-      <c r="H959" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
+      <c r="H959" t="n">
+        <v>22.08</v>
       </c>
     </row>
     <row r="960">
@@ -35129,11 +35127,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H960" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H960" t="inlineStr"/>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -35167,10 +35161,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H961" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H961" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="962">
@@ -35205,10 +35197,8 @@
           <t>2.58%</t>
         </is>
       </c>
-      <c r="H962" t="inlineStr">
-        <is>
-          <t>22.30</t>
-        </is>
+      <c r="H962" t="n">
+        <v>22.3</v>
       </c>
     </row>
     <row r="963">
@@ -35243,10 +35233,8 @@
           <t>3.04%</t>
         </is>
       </c>
-      <c r="H963" t="inlineStr">
-        <is>
-          <t>21.70</t>
-        </is>
+      <c r="H963" t="n">
+        <v>21.7</v>
       </c>
     </row>
     <row r="964">
@@ -35281,10 +35269,8 @@
           <t>3.50%</t>
         </is>
       </c>
-      <c r="H964" t="inlineStr">
-        <is>
-          <t>21.19</t>
-        </is>
+      <c r="H964" t="n">
+        <v>21.19</v>
       </c>
     </row>
     <row r="965">
@@ -35319,10 +35305,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H965" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
+      <c r="H965" t="n">
+        <v>33.61</v>
       </c>
     </row>
     <row r="966">
@@ -35357,10 +35341,8 @@
           <t>1.39%</t>
         </is>
       </c>
-      <c r="H966" t="inlineStr">
-        <is>
-          <t>34.81</t>
-        </is>
+      <c r="H966" t="n">
+        <v>34.81</v>
       </c>
     </row>
     <row r="967">
@@ -35395,10 +35377,8 @@
           <t>3.25%</t>
         </is>
       </c>
-      <c r="H967" t="inlineStr">
-        <is>
-          <t>32.96</t>
-        </is>
+      <c r="H967" t="n">
+        <v>32.96</v>
       </c>
     </row>
     <row r="968">
@@ -35433,10 +35413,8 @@
           <t>9.78%</t>
         </is>
       </c>
-      <c r="H968" t="inlineStr">
-        <is>
-          <t>32.63</t>
-        </is>
+      <c r="H968" t="n">
+        <v>32.63</v>
       </c>
     </row>
     <row r="969">
@@ -35471,9 +35449,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H969" t="inlineStr">
-        <is>
-          <t>35.70</t>
+      <c r="H969" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D970" t="n">
+        <v>0</v>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>216.66%</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>21.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="D971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>15.30%</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="D972" t="n">
+        <v>0</v>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>-5.27%</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>37.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="D973" t="n">
+        <v>0</v>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>165.58%</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>2.58%</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>22.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>49.14%</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>3.01%</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D975" t="n">
+        <v>0</v>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>21.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>179.87%</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>32.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D977" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>-2.09%</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>88.00%</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="D978" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>-2.08%</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>91.45%</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>32.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="D979" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>124.95%</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>9.97%</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>32.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="D980" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>-1.66%</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>66.10%</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>35.11</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>216.66%</t>
+          <t>222.03%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,14 +505,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.35</v>
+        <v>20.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15.30%</t>
+          <t>21.87%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.95</v>
+        <v>29.55</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.27%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.60</t>
+          <t>37.88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.75</v>
+        <v>38.65</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>165.58%</t>
+          <t>161.43%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.27</t>
+          <t>22.21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46.5</v>
+        <v>47.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.14%</t>
+          <t>50.32%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>25.90%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>18.65</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>179.87%</t>
+          <t>197.92%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>34.54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>89.94%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>34.26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96.34999999999999</v>
+        <v>97</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.05</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.45%</t>
+          <t>94.22%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>32.49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.63</v>
+        <v>39.83</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>124.95%</t>
+          <t>129.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>9.92%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.61</v>
+        <v>16.65</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.10%</t>
+          <t>66.50%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>35.19</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H980"/>
+  <dimension ref="A1:H991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35485,10 +35485,8 @@
           <t>1.84%</t>
         </is>
       </c>
-      <c r="H970" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
+      <c r="H970" t="n">
+        <v>21.47</v>
       </c>
     </row>
     <row r="971">
@@ -35523,11 +35521,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H971" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H971" t="inlineStr"/>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -35561,10 +35555,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H972" t="inlineStr">
-        <is>
-          <t>37.60</t>
-        </is>
+      <c r="H972" t="n">
+        <v>37.6</v>
       </c>
     </row>
     <row r="973">
@@ -35599,10 +35591,8 @@
           <t>2.58%</t>
         </is>
       </c>
-      <c r="H973" t="inlineStr">
-        <is>
-          <t>22.27</t>
-        </is>
+      <c r="H973" t="n">
+        <v>22.27</v>
       </c>
     </row>
     <row r="974">
@@ -35637,10 +35627,8 @@
           <t>3.01%</t>
         </is>
       </c>
-      <c r="H974" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
+      <c r="H974" t="n">
+        <v>22.46</v>
       </c>
     </row>
     <row r="975">
@@ -35675,10 +35663,8 @@
           <t>3.44%</t>
         </is>
       </c>
-      <c r="H975" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
+      <c r="H975" t="n">
+        <v>21.85</v>
       </c>
     </row>
     <row r="976">
@@ -35713,10 +35699,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H976" t="inlineStr">
-        <is>
-          <t>32.96</t>
-        </is>
+      <c r="H976" t="n">
+        <v>32.96</v>
       </c>
     </row>
     <row r="977">
@@ -35751,10 +35735,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H977" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
+      <c r="H977" t="n">
+        <v>34.08</v>
       </c>
     </row>
     <row r="978">
@@ -35789,10 +35771,8 @@
           <t>3.32%</t>
         </is>
       </c>
-      <c r="H978" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="H978" t="n">
+        <v>32.28</v>
       </c>
     </row>
     <row r="979">
@@ -35827,10 +35807,8 @@
           <t>9.97%</t>
         </is>
       </c>
-      <c r="H979" t="inlineStr">
-        <is>
-          <t>32.03</t>
-        </is>
+      <c r="H979" t="n">
+        <v>32.03</v>
       </c>
     </row>
     <row r="980">
@@ -35865,9 +35843,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H980" t="inlineStr">
-        <is>
-          <t>35.11</t>
+      <c r="H980" t="n">
+        <v>35.11</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>142</v>
+      </c>
+      <c r="D981" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>222.03%</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D982" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>21.87%</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="D983" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="D984" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>161.43%</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>2.59%</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>22.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D985" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>50.32%</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="D986" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>25.90%</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="D987" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>4.78%</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>197.92%</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>34.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>113</v>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>89.94%</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>34.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>97</v>
+      </c>
+      <c r="D989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>94.22%</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>32.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="D990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>129.06%</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>32.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>66.50%</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>35.19</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142</v>
+        <v>133.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>-8.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>-5.99%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>222.03%</t>
+          <t>205.13%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>20.26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.9</v>
+        <v>20.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.55</v>
+        <v>-0.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.87%</t>
+          <t>19.82%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.55</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.65</v>
+        <v>38.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>161.43%</t>
+          <t>151.52%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>22.07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.3</v>
+        <v>48.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.32%</t>
+          <t>54.38%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.1</v>
+        <v>52.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.90%</t>
+          <t>29.66%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>22.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.65</v>
+        <v>17.95</v>
       </c>
       <c r="D8" t="n">
-        <v>0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>197.92%</t>
+          <t>191.40%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>33.24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>113</v>
+        <v>108.9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,24 +761,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.94%</t>
+          <t>79.79%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>33.02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>97</v>
+        <v>93.3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.22%</t>
+          <t>84.51%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>31.25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39.83</v>
+        <v>38.05</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129.06%</t>
+          <t>115.66%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.92%</t>
+          <t>10.38%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>30.75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.65</v>
+        <v>16.19</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.50%</t>
+          <t>61.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.22</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H991"/>
+  <dimension ref="A1:H1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35879,10 +35879,8 @@
           <t>1.84%</t>
         </is>
       </c>
-      <c r="H981" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
+      <c r="H981" t="n">
+        <v>21.55</v>
       </c>
     </row>
     <row r="982">
@@ -35917,11 +35915,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H982" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H982" t="inlineStr"/>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -35955,10 +35949,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H983" t="inlineStr">
-        <is>
-          <t>37.88</t>
-        </is>
+      <c r="H983" t="n">
+        <v>37.88</v>
       </c>
     </row>
     <row r="984">
@@ -35993,10 +35985,8 @@
           <t>2.59%</t>
         </is>
       </c>
-      <c r="H984" t="inlineStr">
-        <is>
-          <t>22.21</t>
-        </is>
+      <c r="H984" t="n">
+        <v>22.21</v>
       </c>
     </row>
     <row r="985">
@@ -36031,10 +36021,8 @@
           <t>2.96%</t>
         </is>
       </c>
-      <c r="H985" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
+      <c r="H985" t="n">
+        <v>22.85</v>
       </c>
     </row>
     <row r="986">
@@ -36069,10 +36057,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H986" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
+      <c r="H986" t="n">
+        <v>21.65</v>
       </c>
     </row>
     <row r="987">
@@ -36107,10 +36093,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H987" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
+      <c r="H987" t="n">
+        <v>34.54</v>
       </c>
     </row>
     <row r="988">
@@ -36145,10 +36129,8 @@
           <t>1.42%</t>
         </is>
       </c>
-      <c r="H988" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
+      <c r="H988" t="n">
+        <v>34.26</v>
       </c>
     </row>
     <row r="989">
@@ -36183,10 +36165,8 @@
           <t>3.30%</t>
         </is>
       </c>
-      <c r="H989" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="H989" t="n">
+        <v>32.49</v>
       </c>
     </row>
     <row r="990">
@@ -36221,10 +36201,8 @@
           <t>9.92%</t>
         </is>
       </c>
-      <c r="H990" t="inlineStr">
-        <is>
-          <t>32.19</t>
-        </is>
+      <c r="H990" t="n">
+        <v>32.19</v>
       </c>
     </row>
     <row r="991">
@@ -36259,9 +36237,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H991" t="inlineStr">
-        <is>
-          <t>35.19</t>
+      <c r="H991" t="n">
+        <v>35.19</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D992" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>-5.99%</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>205.13%</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>20.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="D993" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>-3.11%</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>19.82%</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>29</v>
+      </c>
+      <c r="D994" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>-2.64%</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>3.45%</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>37.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="D995" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>151.52%</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>22.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="D996" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>54.38%</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>2.87%</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>23.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D997" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>29.66%</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="D998" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>191.40%</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>33.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="D999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>79.79%</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>33.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>84.51%</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>115.66%</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>10.38%</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>61.90%</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>34.22</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>133.5</v>
+        <v>133</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.99%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>205.13%</t>
+          <t>201.28%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.25</v>
+        <v>21.35</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.65</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.82%</t>
+          <t>24.85%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.55</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>37.56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.25</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>151.52%</t>
+          <t>156.11%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48.8</v>
+        <v>49.15</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>0.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>54.38%</t>
+          <t>58.12%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>23.18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.5</v>
+        <v>53.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.66%</t>
+          <t>33.10%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.95</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>191.40%</t>
+          <t>185.26%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>32.96</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.9</v>
+        <v>109</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79.79%</t>
+          <t>76.53%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>33.05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.3</v>
+        <v>94</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -799,24 +799,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>84.51%</t>
+          <t>82.45%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.05</v>
+        <v>38.22</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -837,24 +837,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>115.66%</t>
+          <t>110.64%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.33%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.89</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.19</v>
+        <v>16.2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.90%</t>
+          <t>62.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>34.24</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1002"/>
+  <dimension ref="A1:H1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36273,10 +36273,8 @@
           <t>1.95%</t>
         </is>
       </c>
-      <c r="H992" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
+      <c r="H992" t="n">
+        <v>20.26</v>
       </c>
     </row>
     <row r="993">
@@ -36311,11 +36309,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H993" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H993" t="inlineStr"/>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
@@ -36349,10 +36343,8 @@
           <t>3.45%</t>
         </is>
       </c>
-      <c r="H994" t="inlineStr">
-        <is>
-          <t>37.18</t>
-        </is>
+      <c r="H994" t="n">
+        <v>37.18</v>
       </c>
     </row>
     <row r="995">
@@ -36387,10 +36379,8 @@
           <t>2.60%</t>
         </is>
       </c>
-      <c r="H995" t="inlineStr">
-        <is>
-          <t>22.07</t>
-        </is>
+      <c r="H995" t="n">
+        <v>22.07</v>
       </c>
     </row>
     <row r="996">
@@ -36425,10 +36415,8 @@
           <t>2.87%</t>
         </is>
       </c>
-      <c r="H996" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
+      <c r="H996" t="n">
+        <v>23.02</v>
       </c>
     </row>
     <row r="997">
@@ -36463,10 +36451,8 @@
           <t>3.33%</t>
         </is>
       </c>
-      <c r="H997" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
+      <c r="H997" t="n">
+        <v>22.25</v>
       </c>
     </row>
     <row r="998">
@@ -36501,10 +36487,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H998" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
+      <c r="H998" t="n">
+        <v>33.24</v>
       </c>
     </row>
     <row r="999">
@@ -36539,10 +36523,8 @@
           <t>1.47%</t>
         </is>
       </c>
-      <c r="H999" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
+      <c r="H999" t="n">
+        <v>33.02</v>
       </c>
     </row>
     <row r="1000">
@@ -36577,10 +36559,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H1000" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
+      <c r="H1000" t="n">
+        <v>31.25</v>
       </c>
     </row>
     <row r="1001">
@@ -36615,10 +36595,8 @@
           <t>10.38%</t>
         </is>
       </c>
-      <c r="H1001" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
+      <c r="H1001" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="1002">
@@ -36653,9 +36631,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1002" t="inlineStr">
-        <is>
-          <t>34.22</t>
+      <c r="H1002" t="n">
+        <v>34.22</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>201.28%</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>5.43%</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>24.85%</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>37.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>156.11%</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>58.12%</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>23.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>33.10%</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>185.26%</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>32.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>109</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>76.53%</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>94</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>82.45%</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>31.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>110.64%</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>10.33%</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>30.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>62.00%</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>34.24</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>133</v>
+        <v>131.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>201.28%</t>
+          <t>190.13%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>19.95</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.35</v>
+        <v>20.65</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.85%</t>
+          <t>21.83%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.3</v>
+        <v>28.75</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>-0.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>36.86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.1</v>
+        <v>38.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>156.11%</t>
+          <t>151.80%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>21.95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.15</v>
+        <v>49.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.12%</t>
+          <t>59.26%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>23.28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.10%</t>
+          <t>33.91%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.15</v>
+        <v>-0.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>185.26%</t>
+          <t>179.65%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>32.31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>109</v>
+        <v>108.15</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76.53%</t>
+          <t>74.87%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>32.79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>94</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>82.45%</t>
+          <t>80.37%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.22</v>
+        <v>35.55</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-2.67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-6.99%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.64%</t>
+          <t>95.14%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.33%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>28.73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.2</v>
+        <v>16.07</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.00%</t>
+          <t>60.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.97</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1013"/>
+  <dimension ref="A1:H1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36667,10 +36667,8 @@
           <t>1.96%</t>
         </is>
       </c>
-      <c r="H1003" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
+      <c r="H1003" t="n">
+        <v>20.18</v>
       </c>
     </row>
     <row r="1004">
@@ -36705,11 +36703,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1004" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -36743,10 +36737,8 @@
           <t>3.41%</t>
         </is>
       </c>
-      <c r="H1005" t="inlineStr">
-        <is>
-          <t>37.56</t>
-        </is>
+      <c r="H1005" t="n">
+        <v>37.56</v>
       </c>
     </row>
     <row r="1006">
@@ -36781,10 +36773,8 @@
           <t>2.56%</t>
         </is>
       </c>
-      <c r="H1006" t="inlineStr">
-        <is>
-          <t>22.47</t>
-        </is>
+      <c r="H1006" t="n">
+        <v>22.47</v>
       </c>
     </row>
     <row r="1007">
@@ -36819,10 +36809,8 @@
           <t>2.85%</t>
         </is>
       </c>
-      <c r="H1007" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
+      <c r="H1007" t="n">
+        <v>23.18</v>
       </c>
     </row>
     <row r="1008">
@@ -36857,10 +36845,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H1008" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="H1008" t="n">
+        <v>22.75</v>
       </c>
     </row>
     <row r="1009">
@@ -36895,10 +36881,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1009" t="inlineStr">
-        <is>
-          <t>32.96</t>
-        </is>
+      <c r="H1009" t="n">
+        <v>32.96</v>
       </c>
     </row>
     <row r="1010">
@@ -36933,10 +36917,8 @@
           <t>1.47%</t>
         </is>
       </c>
-      <c r="H1010" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="H1010" t="n">
+        <v>33.05</v>
       </c>
     </row>
     <row r="1011">
@@ -36971,10 +36953,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H1011" t="inlineStr">
-        <is>
-          <t>31.49</t>
-        </is>
+      <c r="H1011" t="n">
+        <v>31.49</v>
       </c>
     </row>
     <row r="1012">
@@ -37009,10 +36989,8 @@
           <t>10.33%</t>
         </is>
       </c>
-      <c r="H1012" t="inlineStr">
-        <is>
-          <t>30.89</t>
-        </is>
+      <c r="H1012" t="n">
+        <v>30.89</v>
       </c>
     </row>
     <row r="1013">
@@ -37047,9 +37025,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1013" t="inlineStr">
-        <is>
-          <t>34.24</t>
+      <c r="H1013" t="n">
+        <v>34.24</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>190.13%</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>19.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>21.83%</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>-4.41%</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>151.80%</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>59.26%</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>23.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>33.91%</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>22.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>179.65%</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>32.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>-0.78%</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>74.87%</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>32.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>80.37%</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>31.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>-6.99%</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>95.14%</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>11.11%</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>28.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>60.70%</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>33.97</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>190.13%</t>
+          <t>180.20%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.65</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.83%</t>
+          <t>21.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.75</v>
+        <v>29.15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.41%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>37.37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.2</v>
+        <v>37.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9</v>
+        <v>-0.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>151.80%</t>
+          <t>145.54%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.35</v>
+        <v>48.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.26%</t>
+          <t>56.03%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>22.81</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.91%</t>
+          <t>32.17%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>22.54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.45</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.35</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>179.65%</t>
+          <t>172.44%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>31.48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.15</v>
+        <v>107.25</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.85</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.87%</t>
+          <t>73.42%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>32.52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80.37%</t>
+          <t>77.85%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>30.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.55</v>
+        <v>35.09</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.67</v>
+        <v>-0.46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-6.99%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.14%</t>
+          <t>103.25%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>16.33%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.07</v>
+        <v>15.93</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.70%</t>
+          <t>59.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>33.67</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1024"/>
+  <dimension ref="A1:H1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37061,10 +37061,8 @@
           <t>1.98%</t>
         </is>
       </c>
-      <c r="H1014" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="H1014" t="n">
+        <v>19.95</v>
       </c>
     </row>
     <row r="1015">
@@ -37099,11 +37097,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1015" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -37137,10 +37131,8 @@
           <t>3.48%</t>
         </is>
       </c>
-      <c r="H1016" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="H1016" t="n">
+        <v>36.86</v>
       </c>
     </row>
     <row r="1017">
@@ -37175,10 +37167,8 @@
           <t>2.62%</t>
         </is>
       </c>
-      <c r="H1017" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="H1017" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="1018">
@@ -37213,10 +37203,8 @@
           <t>2.84%</t>
         </is>
       </c>
-      <c r="H1018" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
+      <c r="H1018" t="n">
+        <v>23.28</v>
       </c>
     </row>
     <row r="1019">
@@ -37251,10 +37239,8 @@
           <t>3.25%</t>
         </is>
       </c>
-      <c r="H1019" t="inlineStr">
-        <is>
-          <t>22.84</t>
-        </is>
+      <c r="H1019" t="n">
+        <v>22.84</v>
       </c>
     </row>
     <row r="1020">
@@ -37289,10 +37275,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1020" t="inlineStr">
-        <is>
-          <t>32.31</t>
-        </is>
+      <c r="H1020" t="n">
+        <v>32.31</v>
       </c>
     </row>
     <row r="1021">
@@ -37327,10 +37311,8 @@
           <t>1.48%</t>
         </is>
       </c>
-      <c r="H1021" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
+      <c r="H1021" t="n">
+        <v>32.79</v>
       </c>
     </row>
     <row r="1022">
@@ -37365,10 +37347,8 @@
           <t>3.44%</t>
         </is>
       </c>
-      <c r="H1022" t="inlineStr">
-        <is>
-          <t>31.19</t>
-        </is>
+      <c r="H1022" t="n">
+        <v>31.19</v>
       </c>
     </row>
     <row r="1023">
@@ -37403,10 +37383,8 @@
           <t>11.11%</t>
         </is>
       </c>
-      <c r="H1023" t="inlineStr">
-        <is>
-          <t>28.73</t>
-        </is>
+      <c r="H1023" t="n">
+        <v>28.73</v>
       </c>
     </row>
     <row r="1024">
@@ -37441,9 +37419,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1024" t="inlineStr">
-        <is>
-          <t>33.97</t>
+      <c r="H1024" t="n">
+        <v>33.97</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>127</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>180.20%</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>19.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>21.53%</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>-3.08%</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>37.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>-2.49%</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>145.54%</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>21.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>-2.03%</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>56.03%</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>32.17%</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>22.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>172.44%</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>73.42%</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>32.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>77.85%</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>103.25%</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>16.33%</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>59.30%</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>33.67</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>180.20%</t>
+          <t>186.45%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>21.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>0.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.53%</t>
+          <t>24.63%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.15</v>
+        <v>29.45</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.76</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.25</v>
+        <v>38.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.95</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>145.54%</t>
+          <t>151.33%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48.35</v>
+        <v>49.2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>0.85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56.03%</t>
+          <t>57.80%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>23.21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.17%</t>
+          <t>33.01%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>22.71</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>172.44%</t>
+          <t>173.30%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>32.04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.25</v>
+        <v>108.15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>74.59%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>28.28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.8</v>
+        <v>93</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.85%</t>
+          <t>79.51%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>26.85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.09</v>
+        <v>35.61</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.46</v>
+        <v>0.52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.25%</t>
+          <t>104.67%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.33%</t>
+          <t>16.09%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>20.74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.93</v>
+        <v>16.08</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.14</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.30%</t>
+          <t>60.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>27.64</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1035"/>
+  <dimension ref="A1:H1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37455,10 +37455,8 @@
           <t>2.05%</t>
         </is>
       </c>
-      <c r="H1025" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
+      <c r="H1025" t="n">
+        <v>19.27</v>
       </c>
     </row>
     <row r="1026">
@@ -37493,11 +37491,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1026" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1026" t="inlineStr"/>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -37531,10 +37525,8 @@
           <t>3.43%</t>
         </is>
       </c>
-      <c r="H1027" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
+      <c r="H1027" t="n">
+        <v>37.37</v>
       </c>
     </row>
     <row r="1028">
@@ -37569,10 +37561,8 @@
           <t>2.68%</t>
         </is>
       </c>
-      <c r="H1028" t="inlineStr">
-        <is>
-          <t>21.41</t>
-        </is>
+      <c r="H1028" t="n">
+        <v>21.41</v>
       </c>
     </row>
     <row r="1029">
@@ -37607,10 +37597,8 @@
           <t>2.90%</t>
         </is>
       </c>
-      <c r="H1029" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
+      <c r="H1029" t="n">
+        <v>22.81</v>
       </c>
     </row>
     <row r="1030">
@@ -37645,10 +37633,8 @@
           <t>3.29%</t>
         </is>
       </c>
-      <c r="H1030" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
+      <c r="H1030" t="n">
+        <v>22.54</v>
       </c>
     </row>
     <row r="1031">
@@ -37683,10 +37669,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1031" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="H1031" t="n">
+        <v>31.48</v>
       </c>
     </row>
     <row r="1032">
@@ -37721,10 +37705,8 @@
           <t>1.49%</t>
         </is>
       </c>
-      <c r="H1032" t="inlineStr">
-        <is>
-          <t>32.52</t>
-        </is>
+      <c r="H1032" t="n">
+        <v>32.52</v>
       </c>
     </row>
     <row r="1033">
@@ -37759,10 +37741,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H1033" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
+      <c r="H1033" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="1034">
@@ -37797,10 +37777,8 @@
           <t>16.33%</t>
         </is>
       </c>
-      <c r="H1034" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
+      <c r="H1034" t="n">
+        <v>28.36</v>
       </c>
     </row>
     <row r="1035">
@@ -37835,9 +37813,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1035" t="inlineStr">
-        <is>
-          <t>33.67</t>
+      <c r="H1035" t="n">
+        <v>33.67</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>128</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>186.45%</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>19.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>24.63%</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>37.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>151.33%</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>21.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>57.80%</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>23.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>33.01%</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>22.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>173.30%</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>32.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>74.59%</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>28.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>93</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>79.51%</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>104.67%</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>16.09%</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>20.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>60.80%</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>27.64</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>125.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>186.45%</t>
+          <t>180.54%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.25</v>
+        <v>20.65</v>
       </c>
       <c r="D3" t="n">
-        <v>0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.63%</t>
+          <t>20.76%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.45</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-4.10%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -581,14 +581,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.69</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.25</v>
+        <v>37.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>151.33%</t>
+          <t>143.41%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>21.70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.2</v>
+        <v>49.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.80%</t>
+          <t>59.07%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>23.47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.01%</t>
+          <t>37.14%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173.30%</t>
+          <t>167.72%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.15</v>
+        <v>106.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>-1.25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.59%</t>
+          <t>73.95%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>27.95</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>-1.35</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.51%</t>
+          <t>77.39%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>26.46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.61</v>
+        <v>34.82</v>
       </c>
       <c r="D11" t="n">
-        <v>0.52</v>
+        <v>-0.79</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.67%</t>
+          <t>101.89%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.09%</t>
+          <t>16.46%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>20.28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.08</v>
+        <v>15.93</v>
       </c>
       <c r="D12" t="n">
-        <v>0.15</v>
+        <v>-0.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.80%</t>
+          <t>59.30%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>27.38</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1046"/>
+  <dimension ref="A1:H1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37849,10 +37849,8 @@
           <t>2.04%</t>
         </is>
       </c>
-      <c r="H1036" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="H1036" t="n">
+        <v>19.42</v>
       </c>
     </row>
     <row r="1037">
@@ -37887,11 +37885,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1037" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1037" t="inlineStr"/>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -37925,10 +37919,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H1038" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="H1038" t="n">
+        <v>37.76</v>
       </c>
     </row>
     <row r="1039">
@@ -37963,10 +37955,8 @@
           <t>2.61%</t>
         </is>
       </c>
-      <c r="H1039" t="inlineStr">
-        <is>
-          <t>21.98</t>
-        </is>
+      <c r="H1039" t="n">
+        <v>21.98</v>
       </c>
     </row>
     <row r="1040">
@@ -38001,10 +37991,8 @@
           <t>2.85%</t>
         </is>
       </c>
-      <c r="H1040" t="inlineStr">
-        <is>
-          <t>23.21</t>
-        </is>
+      <c r="H1040" t="n">
+        <v>23.21</v>
       </c>
     </row>
     <row r="1041">
@@ -38039,10 +38027,8 @@
           <t>3.26%</t>
         </is>
       </c>
-      <c r="H1041" t="inlineStr">
-        <is>
-          <t>22.71</t>
-        </is>
+      <c r="H1041" t="n">
+        <v>22.71</v>
       </c>
     </row>
     <row r="1042">
@@ -38077,10 +38063,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1042" t="inlineStr">
-        <is>
-          <t>32.04</t>
-        </is>
+      <c r="H1042" t="n">
+        <v>32.04</v>
       </c>
     </row>
     <row r="1043">
@@ -38115,10 +38099,8 @@
           <t>1.48%</t>
         </is>
       </c>
-      <c r="H1043" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
+      <c r="H1043" t="n">
+        <v>28.28</v>
       </c>
     </row>
     <row r="1044">
@@ -38153,10 +38135,8 @@
           <t>3.44%</t>
         </is>
       </c>
-      <c r="H1044" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
+      <c r="H1044" t="n">
+        <v>26.85</v>
       </c>
     </row>
     <row r="1045">
@@ -38191,10 +38171,8 @@
           <t>16.09%</t>
         </is>
       </c>
-      <c r="H1045" t="inlineStr">
-        <is>
-          <t>20.74</t>
-        </is>
+      <c r="H1045" t="n">
+        <v>20.74</v>
       </c>
     </row>
     <row r="1046">
@@ -38229,9 +38207,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1046" t="inlineStr">
-        <is>
-          <t>27.64</t>
+      <c r="H1046" t="n">
+        <v>27.64</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>180.54%</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>20.76%</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>-4.10%</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>37.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>-1.31%</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>143.41%</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>59.07%</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>2.99%</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>37.14%</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>23.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>-1.73%</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>167.72%</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>-1.16%</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>73.95%</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>27.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>77.39%</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>26.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>-2.22%</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>101.89%</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>16.46%</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>20.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>59.30%</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>27.38</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,16 +486,16 @@
         <v>125.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>180.54%</t>
+          <t>181.16%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,16 +524,16 @@
         <v>20.65</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.76%</t>
+          <t>23.28%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,16 +562,16 @@
         <v>29.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.10%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,16 +600,16 @@
         <v>37.75</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>143.41%</t>
+          <t>141.90%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>21.95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,16 +638,16 @@
         <v>49.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.07%</t>
+          <t>58.83%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>55.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.14%</t>
+          <t>37.80%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -714,16 +714,16 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>167.72%</t>
+          <t>174.19%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -752,16 +752,16 @@
         <v>106.9</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.95%</t>
+          <t>74.93%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -790,16 +790,16 @@
         <v>91.65000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.39%</t>
+          <t>78.72%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -828,16 +828,16 @@
         <v>34.82</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.89%</t>
+          <t>103.18%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -866,11 +866,11 @@
         <v>15.93</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1057"/>
+  <dimension ref="A1:H1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38243,10 +38243,8 @@
           <t>2.08%</t>
         </is>
       </c>
-      <c r="H1047" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
+      <c r="H1047" t="n">
+        <v>19.04</v>
       </c>
     </row>
     <row r="1048">
@@ -38281,11 +38279,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1048" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1048" t="inlineStr"/>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -38319,10 +38313,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H1049" t="inlineStr">
-        <is>
-          <t>37.69</t>
-        </is>
+      <c r="H1049" t="n">
+        <v>37.69</v>
       </c>
     </row>
     <row r="1050">
@@ -38357,10 +38349,8 @@
           <t>2.65%</t>
         </is>
       </c>
-      <c r="H1050" t="inlineStr">
-        <is>
-          <t>21.70</t>
-        </is>
+      <c r="H1050" t="n">
+        <v>21.7</v>
       </c>
     </row>
     <row r="1051">
@@ -38395,10 +38385,8 @@
           <t>2.81%</t>
         </is>
       </c>
-      <c r="H1051" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="H1051" t="n">
+        <v>23.47</v>
       </c>
     </row>
     <row r="1052">
@@ -38433,10 +38421,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H1052" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
+      <c r="H1052" t="n">
+        <v>23.39</v>
       </c>
     </row>
     <row r="1053">
@@ -38471,10 +38457,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1053" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="H1053" t="n">
+        <v>31.48</v>
       </c>
     </row>
     <row r="1054">
@@ -38509,10 +38493,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H1054" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
+      <c r="H1054" t="n">
+        <v>27.95</v>
       </c>
     </row>
     <row r="1055">
@@ -38547,10 +38529,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H1055" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="H1055" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="1056">
@@ -38585,10 +38565,8 @@
           <t>16.46%</t>
         </is>
       </c>
-      <c r="H1056" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
+      <c r="H1056" t="n">
+        <v>20.28</v>
       </c>
     </row>
     <row r="1057">
@@ -38623,7 +38601,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1057" t="inlineStr">
+      <c r="H1057" t="n">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>181.16%</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>23.28%</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>37.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>141.90%</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>58.83%</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>37.80%</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>23.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>174.19%</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>74.93%</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>27.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>78.72%</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>26.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>103.18%</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>16.46%</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>20.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>59.30%</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
         <is>
           <t>27.38</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,11 +676,11 @@
         <v>55.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -752,11 +752,11 @@
         <v>106.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -790,11 +790,11 @@
         <v>91.65000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -866,11 +866,11 @@
         <v>15.93</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1068"/>
+  <dimension ref="A1:H1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38637,10 +38637,8 @@
           <t>2.08%</t>
         </is>
       </c>
-      <c r="H1058" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
+      <c r="H1058" t="n">
+        <v>19.04</v>
       </c>
     </row>
     <row r="1059">
@@ -38675,11 +38673,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1059" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -38713,10 +38707,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H1060" t="inlineStr">
-        <is>
-          <t>37.69</t>
-        </is>
+      <c r="H1060" t="n">
+        <v>37.69</v>
       </c>
     </row>
     <row r="1061">
@@ -38751,10 +38743,8 @@
           <t>2.65%</t>
         </is>
       </c>
-      <c r="H1061" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="H1061" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="1062">
@@ -38789,10 +38779,8 @@
           <t>2.81%</t>
         </is>
       </c>
-      <c r="H1062" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="H1062" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="1063">
@@ -38827,10 +38815,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H1063" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
+      <c r="H1063" t="n">
+        <v>23.39</v>
       </c>
     </row>
     <row r="1064">
@@ -38865,10 +38851,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1064" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="H1064" t="n">
+        <v>31.48</v>
       </c>
     </row>
     <row r="1065">
@@ -38903,10 +38887,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H1065" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
+      <c r="H1065" t="n">
+        <v>27.95</v>
       </c>
     </row>
     <row r="1066">
@@ -38941,10 +38923,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H1066" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="H1066" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="1067">
@@ -38979,10 +38959,8 @@
           <t>16.46%</t>
         </is>
       </c>
-      <c r="H1067" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
+      <c r="H1067" t="n">
+        <v>20.28</v>
       </c>
     </row>
     <row r="1068">
@@ -39017,7 +38995,423 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1068" t="inlineStr">
+      <c r="H1068" t="n">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>181.16%</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>23.28%</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>37.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>141.90%</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>58.83%</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>37.80%</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>23.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>174.19%</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>74.93%</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>27.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>78.72%</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>26.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>103.18%</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>16.46%</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>20.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>59.30%</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
         <is>
           <t>27.38</t>
         </is>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125.5</v>
+        <v>122.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>181.16%</t>
+          <t>173.24%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.96</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.65</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.28%</t>
+          <t>21.43%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>37.95</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.75</v>
+        <v>38.45</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>141.90%</t>
+          <t>147.16%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>22.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.75</v>
+        <v>49.45</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.83%</t>
+          <t>70.11%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.80%</t>
+          <t>38.47%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>174.19%</t>
+          <t>147.80%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>31.30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.9</v>
+        <v>106.6</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>-0.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.93%</t>
+          <t>70.47%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>27.87</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,19 +787,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>78.72%</t>
+          <t>75.06%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,14 +809,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.82</v>
+        <v>34.72</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.18%</t>
+          <t>97.54%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.46%</t>
+          <t>16.50%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.93</v>
+        <v>15.9</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.30%</t>
+          <t>59.00%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.33</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1079"/>
+  <dimension ref="A1:H1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39031,10 +39031,8 @@
           <t>2.08%</t>
         </is>
       </c>
-      <c r="H1069" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
+      <c r="H1069" t="n">
+        <v>19.04</v>
       </c>
     </row>
     <row r="1070">
@@ -39069,11 +39067,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1070" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1070" t="inlineStr"/>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -39107,10 +39101,8 @@
           <t>3.40%</t>
         </is>
       </c>
-      <c r="H1071" t="inlineStr">
-        <is>
-          <t>37.69</t>
-        </is>
+      <c r="H1071" t="n">
+        <v>37.69</v>
       </c>
     </row>
     <row r="1072">
@@ -39145,10 +39137,8 @@
           <t>2.65%</t>
         </is>
       </c>
-      <c r="H1072" t="inlineStr">
-        <is>
-          <t>21.70</t>
-        </is>
+      <c r="H1072" t="n">
+        <v>21.7</v>
       </c>
     </row>
     <row r="1073">
@@ -39183,10 +39173,8 @@
           <t>2.81%</t>
         </is>
       </c>
-      <c r="H1073" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="H1073" t="n">
+        <v>23.47</v>
       </c>
     </row>
     <row r="1074">
@@ -39204,7 +39192,7 @@
         <v>55.2</v>
       </c>
       <c r="D1074" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E1074" t="inlineStr">
         <is>
@@ -39221,10 +39209,8 @@
           <t>3.17%</t>
         </is>
       </c>
-      <c r="H1074" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
+      <c r="H1074" t="n">
+        <v>23.39</v>
       </c>
     </row>
     <row r="1075">
@@ -39259,10 +39245,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1075" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="H1075" t="n">
+        <v>31.48</v>
       </c>
     </row>
     <row r="1076">
@@ -39280,7 +39264,7 @@
         <v>106.9</v>
       </c>
       <c r="D1076" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
@@ -39297,10 +39281,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H1076" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
+      <c r="H1076" t="n">
+        <v>27.95</v>
       </c>
     </row>
     <row r="1077">
@@ -39318,7 +39300,7 @@
         <v>91.65000000000001</v>
       </c>
       <c r="D1077" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E1077" t="inlineStr">
         <is>
@@ -39335,10 +39317,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H1077" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="H1077" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="1078">
@@ -39373,10 +39353,8 @@
           <t>16.46%</t>
         </is>
       </c>
-      <c r="H1078" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
+      <c r="H1078" t="n">
+        <v>20.28</v>
       </c>
     </row>
     <row r="1079">
@@ -39394,7 +39372,7 @@
         <v>15.93</v>
       </c>
       <c r="D1079" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E1079" t="inlineStr">
         <is>
@@ -39411,9 +39389,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1079" t="inlineStr">
-        <is>
-          <t>27.38</t>
+      <c r="H1079" t="n">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>173.24%</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>21.43%</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>-6.26%</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>147.16%</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>70.11%</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>2.83%</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>23.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>38.47%</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>3.18%</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>23.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>147.80%</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>31.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>70.47%</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>27.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>75.06%</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>26.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>97.54%</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>16.50%</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>20.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>59.00%</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>27.33</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122.5</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>-3</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>173.24%</t>
+          <t>183.02%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>20.55</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.43%</t>
+          <t>24.17%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.6</v>
+        <v>29.85</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>38.27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.45</v>
+        <v>38.55</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>147.16%</t>
+          <t>148.57%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.10</t>
+          <t>22.16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.45</v>
+        <v>48.35</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.11%</t>
+          <t>67.99%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>22.81</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>53.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.47%</t>
+          <t>36.53%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>22.84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9</v>
+        <v>17.15</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>147.80%</t>
+          <t>141.55%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.30</t>
+          <t>31.76</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>106.6</v>
+        <v>108.65</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3</v>
+        <v>2.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.47%</t>
+          <t>74.99%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>28.41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>1.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.06%</t>
+          <t>79.02%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>27.02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.72</v>
+        <v>35.87</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>1.15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>97.54%</t>
+          <t>104.77%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.50%</t>
+          <t>15.97%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>20.89</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.9</v>
+        <v>16.17</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.00%</t>
+          <t>61.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.79</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1090"/>
+  <dimension ref="A1:H1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39425,10 +39425,8 @@
           <t>2.13%</t>
         </is>
       </c>
-      <c r="H1080" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
+      <c r="H1080" t="n">
+        <v>18.96</v>
       </c>
     </row>
     <row r="1081">
@@ -39463,11 +39461,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1081" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1081" t="inlineStr"/>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -39501,10 +39495,8 @@
           <t>3.38%</t>
         </is>
       </c>
-      <c r="H1082" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
+      <c r="H1082" t="n">
+        <v>37.95</v>
       </c>
     </row>
     <row r="1083">
@@ -39539,10 +39531,8 @@
           <t>2.60%</t>
         </is>
       </c>
-      <c r="H1083" t="inlineStr">
-        <is>
-          <t>22.10</t>
-        </is>
+      <c r="H1083" t="n">
+        <v>22.1</v>
       </c>
     </row>
     <row r="1084">
@@ -39577,10 +39567,8 @@
           <t>2.83%</t>
         </is>
       </c>
-      <c r="H1084" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="H1084" t="n">
+        <v>23.33</v>
       </c>
     </row>
     <row r="1085">
@@ -39615,10 +39603,8 @@
           <t>3.18%</t>
         </is>
       </c>
-      <c r="H1085" t="inlineStr">
-        <is>
-          <t>23.31</t>
-        </is>
+      <c r="H1085" t="n">
+        <v>23.31</v>
       </c>
     </row>
     <row r="1086">
@@ -39653,10 +39639,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1086" t="inlineStr">
-        <is>
-          <t>31.30</t>
-        </is>
+      <c r="H1086" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="1087">
@@ -39691,10 +39675,8 @@
           <t>1.50%</t>
         </is>
       </c>
-      <c r="H1087" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
+      <c r="H1087" t="n">
+        <v>27.87</v>
       </c>
     </row>
     <row r="1088">
@@ -39729,10 +39711,8 @@
           <t>3.49%</t>
         </is>
       </c>
-      <c r="H1088" t="inlineStr">
-        <is>
-          <t>26.47</t>
-        </is>
+      <c r="H1088" t="n">
+        <v>26.47</v>
       </c>
     </row>
     <row r="1089">
@@ -39767,10 +39747,8 @@
           <t>16.50%</t>
         </is>
       </c>
-      <c r="H1089" t="inlineStr">
-        <is>
-          <t>20.22</t>
-        </is>
+      <c r="H1089" t="n">
+        <v>20.22</v>
       </c>
     </row>
     <row r="1090">
@@ -39805,9 +39783,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1090" t="inlineStr">
-        <is>
-          <t>27.33</t>
+      <c r="H1090" t="n">
+        <v>27.33</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>128</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>4.49%</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>183.02%</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>19.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>24.17%</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>-5.47%</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>38.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>148.57%</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>2.59%</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>22.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>-2.22%</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>67.99%</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>36.53%</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>22.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>141.55%</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>31.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>74.99%</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>79.02%</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>3.42%</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>27.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>3.31%</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>104.77%</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>15.97%</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>20.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>61.70%</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>27.79</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>115.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>-12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>183.02%</t>
+          <t>157.62%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>17.24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.55</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.15</v>
+        <v>-0.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.17%</t>
+          <t>16.62%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.85</v>
+        <v>32.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>2.95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>9.88%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.47%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>42.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.55</v>
+        <v>38.5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>148.57%</t>
+          <t>149.02%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>22.13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48.35</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1</v>
+        <v>0.65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>67.99%</t>
+          <t>69.12%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>23.11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -673,36 +673,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>53.9</v>
+        <v>54.8</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.53%</t>
+          <t>39.66%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>23.22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.15</v>
+        <v>16.75</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>141.55%</t>
+          <t>139.63%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108.65</v>
+        <v>107.25</v>
       </c>
       <c r="D9" t="n">
-        <v>2.05</v>
+        <v>-1.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.99%</t>
+          <t>69.92%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>28.04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.02%</t>
+          <t>74.08%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.87</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
-        <v>1.15</v>
+        <v>-0.87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.77%</t>
+          <t>96.68%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.97%</t>
+          <t>16.37%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>20.38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.17</v>
+        <v>16.01</v>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>-0.16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.70%</t>
+          <t>60.10%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.52</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1101"/>
+  <dimension ref="A1:H1112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39819,10 +39819,8 @@
           <t>2.04%</t>
         </is>
       </c>
-      <c r="H1091" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="H1091" t="n">
+        <v>19.42</v>
       </c>
     </row>
     <row r="1092">
@@ -39857,11 +39855,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1092" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1092" t="inlineStr"/>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -39895,10 +39889,8 @@
           <t>3.35%</t>
         </is>
       </c>
-      <c r="H1093" t="inlineStr">
-        <is>
-          <t>38.27</t>
-        </is>
+      <c r="H1093" t="n">
+        <v>38.27</v>
       </c>
     </row>
     <row r="1094">
@@ -39933,10 +39925,8 @@
           <t>2.59%</t>
         </is>
       </c>
-      <c r="H1094" t="inlineStr">
-        <is>
-          <t>22.16</t>
-        </is>
+      <c r="H1094" t="n">
+        <v>22.16</v>
       </c>
     </row>
     <row r="1095">
@@ -39971,10 +39961,8 @@
           <t>2.90%</t>
         </is>
       </c>
-      <c r="H1095" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
+      <c r="H1095" t="n">
+        <v>22.81</v>
       </c>
     </row>
     <row r="1096">
@@ -40009,10 +39997,8 @@
           <t>3.25%</t>
         </is>
       </c>
-      <c r="H1096" t="inlineStr">
-        <is>
-          <t>22.84</t>
-        </is>
+      <c r="H1096" t="n">
+        <v>22.84</v>
       </c>
     </row>
     <row r="1097">
@@ -40047,10 +40033,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1097" t="inlineStr">
-        <is>
-          <t>31.76</t>
-        </is>
+      <c r="H1097" t="n">
+        <v>31.76</v>
       </c>
     </row>
     <row r="1098">
@@ -40085,10 +40069,8 @@
           <t>1.47%</t>
         </is>
       </c>
-      <c r="H1098" t="inlineStr">
-        <is>
-          <t>28.41</t>
-        </is>
+      <c r="H1098" t="n">
+        <v>28.41</v>
       </c>
     </row>
     <row r="1099">
@@ -40123,10 +40105,8 @@
           <t>3.42%</t>
         </is>
       </c>
-      <c r="H1099" t="inlineStr">
-        <is>
-          <t>27.02</t>
-        </is>
+      <c r="H1099" t="n">
+        <v>27.02</v>
       </c>
     </row>
     <row r="1100">
@@ -40161,10 +40141,8 @@
           <t>15.97%</t>
         </is>
       </c>
-      <c r="H1100" t="inlineStr">
-        <is>
-          <t>20.89</t>
-        </is>
+      <c r="H1100" t="n">
+        <v>20.89</v>
       </c>
     </row>
     <row r="1101">
@@ -40199,9 +40177,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1101" t="inlineStr">
-        <is>
-          <t>27.79</t>
+      <c r="H1101" t="n">
+        <v>27.79</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>-9.77%</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>157.62%</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>17.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>-2.68%</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>16.62%</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>9.88%</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>2.77%</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>149.02%</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>22.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>69.12%</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>23.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>39.66%</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>-2.33%</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>139.63%</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>31.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>69.92%</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>28.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>74.08%</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>3.47%</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>26.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>35</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>96.68%</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>16.37%</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>20.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>60.10%</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>27.52</t>
         </is>
       </c>
     </row>

--- a/0050_history.xlsx
+++ b/0050_history.xlsx
@@ -474,7 +474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,36 +483,36 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>115.5</v>
+        <v>111.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.5</v>
+        <v>-4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>157.62%</t>
+          <t>147.35%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>16.64</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,19 +521,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.62%</t>
+          <t>11.49%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,36 +559,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.95</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.88%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>10.08%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,36 +597,36 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.5</v>
+        <v>37.8</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>149.02%</t>
+          <t>145.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>21.72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -635,36 +635,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>49.05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.12%</t>
+          <t>71.57%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>23.14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -676,16 +676,16 @@
         <v>54.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.66%</t>
+          <t>38.81%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.75</v>
+        <v>16.35</v>
       </c>
       <c r="D8" t="n">
         <v>-0.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>139.63%</t>
+          <t>139.04%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,14 +733,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>30.28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>107.25</v>
+        <v>104.95</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4</v>
+        <v>-2.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.92%</t>
+          <t>66.27%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>27.44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -787,36 +787,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.09999999999999</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5</v>
+        <v>-2.25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.08%</t>
+          <t>69.98%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>25.94</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -825,36 +825,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>33.84</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.87</v>
+        <v>-1.16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>96.68%</t>
+          <t>89.45%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.37%</t>
+          <t>16.93%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>19.71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.01</v>
+        <v>15.67</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.16</v>
+        <v>-0.34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.10%</t>
+          <t>56.70%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>26.93</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1112"/>
+  <dimension ref="A1:H1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40213,10 +40213,8 @@
           <t>2.26%</t>
         </is>
       </c>
-      <c r="H1102" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="H1102" t="n">
+        <v>17.24</v>
       </c>
     </row>
     <row r="1103">
@@ -40251,11 +40249,7 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H1103" t="inlineStr"/>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -40289,10 +40283,8 @@
           <t>3.05%</t>
         </is>
       </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>42.05</t>
-        </is>
+      <c r="H1104" t="n">
+        <v>42.05</v>
       </c>
     </row>
     <row r="1105">
@@ -40327,10 +40319,8 @@
           <t>2.60%</t>
         </is>
       </c>
-      <c r="H1105" t="inlineStr">
-        <is>
-          <t>22.13</t>
-        </is>
+      <c r="H1105" t="n">
+        <v>22.13</v>
       </c>
     </row>
     <row r="1106">
@@ -40365,10 +40355,8 @@
           <t>2.86%</t>
         </is>
       </c>
-      <c r="H1106" t="inlineStr">
-        <is>
-          <t>23.11</t>
-        </is>
+      <c r="H1106" t="n">
+        <v>23.11</v>
       </c>
     </row>
     <row r="1107">
@@ -40403,10 +40391,8 @@
           <t>3.19%</t>
         </is>
       </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>23.22</t>
-        </is>
+      <c r="H1107" t="n">
+        <v>23.22</v>
       </c>
     </row>
     <row r="1108">
@@ -40441,10 +40427,8 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1108" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
+      <c r="H1108" t="n">
+        <v>31.02</v>
       </c>
     </row>
     <row r="1109">
@@ -40479,10 +40463,8 @@
           <t>1.49%</t>
         </is>
       </c>
-      <c r="H1109" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
+      <c r="H1109" t="n">
+        <v>28.04</v>
       </c>
     </row>
     <row r="1110">
@@ -40517,10 +40499,8 @@
           <t>3.47%</t>
         </is>
       </c>
-      <c r="H1110" t="inlineStr">
-        <is>
-          <t>26.59</t>
-        </is>
+      <c r="H1110" t="n">
+        <v>26.59</v>
       </c>
     </row>
     <row r="1111">
@@ -40555,10 +40535,8 @@
           <t>16.37%</t>
         </is>
       </c>
-      <c r="H1111" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
+      <c r="H1111" t="n">
+        <v>20.38</v>
       </c>
     </row>
     <row r="1112">
@@ -40593,9 +40571,425 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H1112" t="inlineStr">
-        <is>
-          <t>27.52</t>
+      <c r="H1112" t="n">
+        <v>27.52</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>聯電(2303)</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>-3.46%</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>147.35%</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>16.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>友訊(2332)</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>11.49%</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>佳世達(2352)</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>10.08%</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>43.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>開發金(2883)</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>-1.82%</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>145.26%</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>21.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>玉山金(2884)</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>71.57%</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>23.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>兆豐金(2886)</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>38.81%</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>聯合再生(3576)</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>139.04%</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>30.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>台灣50(0050)</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>-2.14%</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>66.27%</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>27.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>ESG永續(00850)</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>-2.44%</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>69.98%</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>3.56%</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>25.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>半導體收益(00927)</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>-3.31%</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>89.45%</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>16.93%</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>19.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>凱基TOP50(009816)</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>-2.12%</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>56.70%</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>26.93</t>
         </is>
       </c>
     </row>
